--- a/光伏配储项目/电价数据/2026/音山站.xlsx
+++ b/光伏配储项目/电价数据/2026/音山站.xlsx
@@ -16,10 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy/mm/dd"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -64,7 +63,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,13 +429,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CS116"/>
+  <dimension ref="A1:CS143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>日期</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -34613,6 +34612,7917 @@
       </c>
       <c r="CS116" t="n">
         <v>0.50979</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="B117" t="n">
+        <v>0.38215</v>
+      </c>
+      <c r="C117" t="n">
+        <v>0.6940299999999999</v>
+      </c>
+      <c r="D117" t="n">
+        <v>0.56325</v>
+      </c>
+      <c r="E117" t="n">
+        <v>0.49852</v>
+      </c>
+      <c r="F117" t="n">
+        <v>0.44409</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0.43848</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0.43791</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0.45473</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0.43932</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0.42326</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0.41939</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0.40894</v>
+      </c>
+      <c r="N117" t="n">
+        <v>0.39852</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0.40029</v>
+      </c>
+      <c r="P117" t="n">
+        <v>0.38533</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>0.40217</v>
+      </c>
+      <c r="R117" t="n">
+        <v>0.42346</v>
+      </c>
+      <c r="S117" t="n">
+        <v>0.41295</v>
+      </c>
+      <c r="T117" t="n">
+        <v>0.35497</v>
+      </c>
+      <c r="U117" t="n">
+        <v>0.39188</v>
+      </c>
+      <c r="V117" t="n">
+        <v>0.38514</v>
+      </c>
+      <c r="W117" t="n">
+        <v>0.41734</v>
+      </c>
+      <c r="X117" t="n">
+        <v>0.39204</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>0.42076</v>
+      </c>
+      <c r="Z117" t="n">
+        <v>0.41431</v>
+      </c>
+      <c r="AA117" t="n">
+        <v>0.4243</v>
+      </c>
+      <c r="AB117" t="n">
+        <v>0.41308</v>
+      </c>
+      <c r="AC117" t="n">
+        <v>0.4443</v>
+      </c>
+      <c r="AD117" t="n">
+        <v>0.35733</v>
+      </c>
+      <c r="AE117" t="n">
+        <v>0.29988</v>
+      </c>
+      <c r="AF117" t="n">
+        <v>0.33396</v>
+      </c>
+      <c r="AG117" t="n">
+        <v>0.30828</v>
+      </c>
+      <c r="AH117" t="n">
+        <v>0.26095</v>
+      </c>
+      <c r="AI117" t="n">
+        <v>0.29484</v>
+      </c>
+      <c r="AJ117" t="n">
+        <v>0.2977</v>
+      </c>
+      <c r="AK117" t="n">
+        <v>0.1989</v>
+      </c>
+      <c r="AL117" t="n">
+        <v>0.24864</v>
+      </c>
+      <c r="AM117" t="n">
+        <v>0.06936</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>0.05757</v>
+      </c>
+      <c r="AO117" t="n">
+        <v>0.04197</v>
+      </c>
+      <c r="AP117" t="n">
+        <v>0.0209</v>
+      </c>
+      <c r="AQ117" t="n">
+        <v>0.04223</v>
+      </c>
+      <c r="AR117" t="n">
+        <v>0.03809000000000001</v>
+      </c>
+      <c r="AS117" t="n">
+        <v>0.03607</v>
+      </c>
+      <c r="AT117" t="n">
+        <v>-0.01167</v>
+      </c>
+      <c r="AU117" t="n">
+        <v>-0.04919</v>
+      </c>
+      <c r="AV117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW117" t="n">
+        <v>0.08543000000000001</v>
+      </c>
+      <c r="AX117" t="n">
+        <v>-0.02191</v>
+      </c>
+      <c r="AY117" t="n">
+        <v>-0.01416</v>
+      </c>
+      <c r="AZ117" t="n">
+        <v>0.00138</v>
+      </c>
+      <c r="BA117" t="n">
+        <v>0.14463</v>
+      </c>
+      <c r="BB117" t="n">
+        <v>0.2126</v>
+      </c>
+      <c r="BC117" t="n">
+        <v>0.23507</v>
+      </c>
+      <c r="BD117" t="n">
+        <v>0.18382</v>
+      </c>
+      <c r="BE117" t="n">
+        <v>0.09673999999999999</v>
+      </c>
+      <c r="BF117" t="n">
+        <v>-0.02967</v>
+      </c>
+      <c r="BG117" t="n">
+        <v>-0.0103</v>
+      </c>
+      <c r="BH117" t="n">
+        <v>0.10167</v>
+      </c>
+      <c r="BI117" t="n">
+        <v>0.11506</v>
+      </c>
+      <c r="BJ117" t="n">
+        <v>0.16213</v>
+      </c>
+      <c r="BK117" t="n">
+        <v>0.21347</v>
+      </c>
+      <c r="BL117" t="n">
+        <v>0.15073</v>
+      </c>
+      <c r="BM117" t="n">
+        <v>0.1277</v>
+      </c>
+      <c r="BN117" t="n">
+        <v>0.10862</v>
+      </c>
+      <c r="BO117" t="n">
+        <v>0.17471</v>
+      </c>
+      <c r="BP117" t="n">
+        <v>0.20782</v>
+      </c>
+      <c r="BQ117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BR117" t="n">
+        <v>0.17549</v>
+      </c>
+      <c r="BS117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BT117" t="n">
+        <v>0.35055</v>
+      </c>
+      <c r="BU117" t="n">
+        <v>0.43234</v>
+      </c>
+      <c r="BV117" t="n">
+        <v>0.35509</v>
+      </c>
+      <c r="BW117" t="n">
+        <v>0.42775</v>
+      </c>
+      <c r="BX117" t="n">
+        <v>0.34133</v>
+      </c>
+      <c r="BY117" t="n">
+        <v>0.5206900000000001</v>
+      </c>
+      <c r="BZ117" t="n">
+        <v>0.33208</v>
+      </c>
+      <c r="CA117" t="n">
+        <v>0.46371</v>
+      </c>
+      <c r="CB117" t="n">
+        <v>0.7267</v>
+      </c>
+      <c r="CC117" t="n">
+        <v>0.6091599999999999</v>
+      </c>
+      <c r="CD117" t="n">
+        <v>0.4936</v>
+      </c>
+      <c r="CE117" t="n">
+        <v>0.47319</v>
+      </c>
+      <c r="CF117" t="n">
+        <v>-0.0195</v>
+      </c>
+      <c r="CG117" t="n">
+        <v>0.37524</v>
+      </c>
+      <c r="CH117" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="CI117" t="n">
+        <v>0.52822</v>
+      </c>
+      <c r="CJ117" t="n">
+        <v>0.18863</v>
+      </c>
+      <c r="CK117" t="n">
+        <v>0.48525</v>
+      </c>
+      <c r="CL117" t="n">
+        <v>0.48974</v>
+      </c>
+      <c r="CM117" t="n">
+        <v>0.58582</v>
+      </c>
+      <c r="CN117" t="n">
+        <v>0.54387</v>
+      </c>
+      <c r="CO117" t="n">
+        <v>0.42594</v>
+      </c>
+      <c r="CP117" t="n">
+        <v>0.47904</v>
+      </c>
+      <c r="CQ117" t="n">
+        <v>0.40085</v>
+      </c>
+      <c r="CR117" t="n">
+        <v>0.41165</v>
+      </c>
+      <c r="CS117" t="n">
+        <v>0.42071</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B118" t="n">
+        <v>0.33018</v>
+      </c>
+      <c r="C118" t="n">
+        <v>0.61227</v>
+      </c>
+      <c r="D118" t="n">
+        <v>1.40662</v>
+      </c>
+      <c r="E118" t="n">
+        <v>0.7411799999999999</v>
+      </c>
+      <c r="F118" t="n">
+        <v>0.96562</v>
+      </c>
+      <c r="G118" t="n">
+        <v>0.79944</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0.5371</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0.5240499999999999</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0.50666</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0.5042300000000001</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0.50244</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0.39314</v>
+      </c>
+      <c r="N118" t="n">
+        <v>0.47441</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0.37267</v>
+      </c>
+      <c r="P118" t="n">
+        <v>0.38122</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>0.39249</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0.3379</v>
+      </c>
+      <c r="S118" t="n">
+        <v>0.37166</v>
+      </c>
+      <c r="T118" t="n">
+        <v>0.35712</v>
+      </c>
+      <c r="U118" t="n">
+        <v>0.36029</v>
+      </c>
+      <c r="V118" t="n">
+        <v>0.3766</v>
+      </c>
+      <c r="W118" t="n">
+        <v>0.37652</v>
+      </c>
+      <c r="X118" t="n">
+        <v>0.36052</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>0.38146</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>0.42301</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>0.5168700000000001</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>0.6296799999999999</v>
+      </c>
+      <c r="AC118" t="n">
+        <v>0.72175</v>
+      </c>
+      <c r="AD118" t="n">
+        <v>0.43755</v>
+      </c>
+      <c r="AE118" t="n">
+        <v>0.3533</v>
+      </c>
+      <c r="AF118" t="n">
+        <v>0.38499</v>
+      </c>
+      <c r="AG118" t="n">
+        <v>0.34582</v>
+      </c>
+      <c r="AH118" t="n">
+        <v>0.32262</v>
+      </c>
+      <c r="AI118" t="n">
+        <v>0.3217</v>
+      </c>
+      <c r="AJ118" t="n">
+        <v>0.4385</v>
+      </c>
+      <c r="AK118" t="n">
+        <v>0.07959000000000001</v>
+      </c>
+      <c r="AL118" t="n">
+        <v>0.30741</v>
+      </c>
+      <c r="AM118" t="n">
+        <v>0.29461</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AO118" t="n">
+        <v>0.25459</v>
+      </c>
+      <c r="AP118" t="n">
+        <v>0.29603</v>
+      </c>
+      <c r="AQ118" t="n">
+        <v>0.26224</v>
+      </c>
+      <c r="AR118" t="n">
+        <v>0.2675</v>
+      </c>
+      <c r="AS118" t="n">
+        <v>0.31138</v>
+      </c>
+      <c r="AT118" t="n">
+        <v>0.22779</v>
+      </c>
+      <c r="AU118" t="n">
+        <v>0.35318</v>
+      </c>
+      <c r="AV118" t="n">
+        <v>0.58533</v>
+      </c>
+      <c r="AW118" t="n">
+        <v>0.07590999999999999</v>
+      </c>
+      <c r="AX118" t="n">
+        <v>0.27115</v>
+      </c>
+      <c r="AY118" t="n">
+        <v>0.26175</v>
+      </c>
+      <c r="AZ118" t="n">
+        <v>0.28728</v>
+      </c>
+      <c r="BA118" t="n">
+        <v>0.29186</v>
+      </c>
+      <c r="BB118" t="n">
+        <v>0.23365</v>
+      </c>
+      <c r="BC118" t="n">
+        <v>0.56137</v>
+      </c>
+      <c r="BD118" t="n">
+        <v>0.3778</v>
+      </c>
+      <c r="BE118" t="n">
+        <v>0.34369</v>
+      </c>
+      <c r="BF118" t="n">
+        <v>-0.03534</v>
+      </c>
+      <c r="BG118" t="n">
+        <v>0.27115</v>
+      </c>
+      <c r="BH118" t="n">
+        <v>0.29866</v>
+      </c>
+      <c r="BI118" t="n">
+        <v>0.30543</v>
+      </c>
+      <c r="BJ118" t="n">
+        <v>0.29761</v>
+      </c>
+      <c r="BK118" t="n">
+        <v>0.30461</v>
+      </c>
+      <c r="BL118" t="n">
+        <v>0.29632</v>
+      </c>
+      <c r="BM118" t="n">
+        <v>0.21967</v>
+      </c>
+      <c r="BN118" t="n">
+        <v>0.15844</v>
+      </c>
+      <c r="BO118" t="n">
+        <v>0.22184</v>
+      </c>
+      <c r="BP118" t="n">
+        <v>0.22527</v>
+      </c>
+      <c r="BQ118" t="n">
+        <v>0.23086</v>
+      </c>
+      <c r="BR118" t="n">
+        <v>0.24988</v>
+      </c>
+      <c r="BS118" t="n">
+        <v>0.39434</v>
+      </c>
+      <c r="BT118" t="n">
+        <v>0.39929</v>
+      </c>
+      <c r="BU118" t="n">
+        <v>0.29008</v>
+      </c>
+      <c r="BV118" t="n">
+        <v>0.22167</v>
+      </c>
+      <c r="BW118" t="n">
+        <v>0.32201</v>
+      </c>
+      <c r="BX118" t="n">
+        <v>0.30759</v>
+      </c>
+      <c r="BY118" t="n">
+        <v>0.41095</v>
+      </c>
+      <c r="BZ118" t="n">
+        <v>0.21984</v>
+      </c>
+      <c r="CA118" t="n">
+        <v>0.6863400000000001</v>
+      </c>
+      <c r="CB118" t="n">
+        <v>0.7944099999999999</v>
+      </c>
+      <c r="CC118" t="n">
+        <v>0.78704</v>
+      </c>
+      <c r="CD118" t="n">
+        <v>0.20403</v>
+      </c>
+      <c r="CE118" t="n">
+        <v>0.31082</v>
+      </c>
+      <c r="CF118" t="n">
+        <v>0.8029700000000001</v>
+      </c>
+      <c r="CG118" t="n">
+        <v>0.30338</v>
+      </c>
+      <c r="CH118" t="n">
+        <v>0.36055</v>
+      </c>
+      <c r="CI118" t="n">
+        <v>0.75709</v>
+      </c>
+      <c r="CJ118" t="n">
+        <v>0.27949</v>
+      </c>
+      <c r="CK118" t="n">
+        <v>0.43542</v>
+      </c>
+      <c r="CL118" t="n">
+        <v>0.5900700000000001</v>
+      </c>
+      <c r="CM118" t="n">
+        <v>0.43879</v>
+      </c>
+      <c r="CN118" t="n">
+        <v>0.43302</v>
+      </c>
+      <c r="CO118" t="n">
+        <v>0.40684</v>
+      </c>
+      <c r="CP118" t="n">
+        <v>0.3325</v>
+      </c>
+      <c r="CQ118" t="n">
+        <v>0.37565</v>
+      </c>
+      <c r="CR118" t="n">
+        <v>0.35271</v>
+      </c>
+      <c r="CS118" t="n">
+        <v>0.33305</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B119" t="n">
+        <v>0.3216</v>
+      </c>
+      <c r="C119" t="n">
+        <v>0.5156000000000001</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0.3691</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0.4672</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0.36216</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0.38062</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0.40136</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0.38371</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0.39059</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0.38069</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0.36034</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0.43251</v>
+      </c>
+      <c r="N119" t="n">
+        <v>0.44862</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0.33512</v>
+      </c>
+      <c r="P119" t="n">
+        <v>0.37126</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>0.39283</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0.36369</v>
+      </c>
+      <c r="S119" t="n">
+        <v>0.36992</v>
+      </c>
+      <c r="T119" t="n">
+        <v>0.35207</v>
+      </c>
+      <c r="U119" t="n">
+        <v>0.35736</v>
+      </c>
+      <c r="V119" t="n">
+        <v>0.34713</v>
+      </c>
+      <c r="W119" t="n">
+        <v>0.36142</v>
+      </c>
+      <c r="X119" t="n">
+        <v>0.3549</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>0.37817</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>0.39646</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>0.47403</v>
+      </c>
+      <c r="AB119" t="n">
+        <v>0.44827</v>
+      </c>
+      <c r="AC119" t="n">
+        <v>0.44264</v>
+      </c>
+      <c r="AD119" t="n">
+        <v>0.3481</v>
+      </c>
+      <c r="AE119" t="n">
+        <v>0.39566</v>
+      </c>
+      <c r="AF119" t="n">
+        <v>0.35246</v>
+      </c>
+      <c r="AG119" t="n">
+        <v>0.36769</v>
+      </c>
+      <c r="AH119" t="n">
+        <v>0.34583</v>
+      </c>
+      <c r="AI119" t="n">
+        <v>0.27308</v>
+      </c>
+      <c r="AJ119" t="n">
+        <v>0.28279</v>
+      </c>
+      <c r="AK119" t="n">
+        <v>0.27818</v>
+      </c>
+      <c r="AL119" t="n">
+        <v>0.30776</v>
+      </c>
+      <c r="AM119" t="n">
+        <v>0.12815</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>0.27366</v>
+      </c>
+      <c r="AO119" t="n">
+        <v>0.24825</v>
+      </c>
+      <c r="AP119" t="n">
+        <v>0.30421</v>
+      </c>
+      <c r="AQ119" t="n">
+        <v>0.30779</v>
+      </c>
+      <c r="AR119" t="n">
+        <v>0.29439</v>
+      </c>
+      <c r="AS119" t="n">
+        <v>0.28118</v>
+      </c>
+      <c r="AT119" t="n">
+        <v>0.33587</v>
+      </c>
+      <c r="AU119" t="n">
+        <v>0.39898</v>
+      </c>
+      <c r="AV119" t="n">
+        <v>0.34878</v>
+      </c>
+      <c r="AW119" t="n">
+        <v>0.3866</v>
+      </c>
+      <c r="AX119" t="n">
+        <v>0.23323</v>
+      </c>
+      <c r="AY119" t="n">
+        <v>0.39301</v>
+      </c>
+      <c r="AZ119" t="n">
+        <v>0.25121</v>
+      </c>
+      <c r="BA119" t="n">
+        <v>0.27936</v>
+      </c>
+      <c r="BB119" t="n">
+        <v>0.05827</v>
+      </c>
+      <c r="BC119" t="n">
+        <v>0.20261</v>
+      </c>
+      <c r="BD119" t="n">
+        <v>0.13159</v>
+      </c>
+      <c r="BE119" t="n">
+        <v>0.19111</v>
+      </c>
+      <c r="BF119" t="n">
+        <v>0.17955</v>
+      </c>
+      <c r="BG119" t="n">
+        <v>0.24344</v>
+      </c>
+      <c r="BH119" t="n">
+        <v>0.29199</v>
+      </c>
+      <c r="BI119" t="n">
+        <v>0.33536</v>
+      </c>
+      <c r="BJ119" t="n">
+        <v>0.29879</v>
+      </c>
+      <c r="BK119" t="n">
+        <v>0.27956</v>
+      </c>
+      <c r="BL119" t="n">
+        <v>0.32154</v>
+      </c>
+      <c r="BM119" t="n">
+        <v>0.3127799999999999</v>
+      </c>
+      <c r="BN119" t="n">
+        <v>0.25867</v>
+      </c>
+      <c r="BO119" t="n">
+        <v>0.29955</v>
+      </c>
+      <c r="BP119" t="n">
+        <v>0.26326</v>
+      </c>
+      <c r="BQ119" t="n">
+        <v>0.21066</v>
+      </c>
+      <c r="BR119" t="n">
+        <v>0.16931</v>
+      </c>
+      <c r="BS119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BT119" t="n">
+        <v>0.26933</v>
+      </c>
+      <c r="BU119" t="n">
+        <v>0.30298</v>
+      </c>
+      <c r="BV119" t="n">
+        <v>0.30199</v>
+      </c>
+      <c r="BW119" t="n">
+        <v>0.31602</v>
+      </c>
+      <c r="BX119" t="n">
+        <v>0.33398</v>
+      </c>
+      <c r="BY119" t="n">
+        <v>0.45744</v>
+      </c>
+      <c r="BZ119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CA119" t="n">
+        <v>0.48719</v>
+      </c>
+      <c r="CB119" t="n">
+        <v>0.31073</v>
+      </c>
+      <c r="CC119" t="n">
+        <v>0.2914</v>
+      </c>
+      <c r="CD119" t="n">
+        <v>0.28536</v>
+      </c>
+      <c r="CE119" t="n">
+        <v>0.25801</v>
+      </c>
+      <c r="CF119" t="n">
+        <v>0.30228</v>
+      </c>
+      <c r="CG119" t="n">
+        <v>0.26595</v>
+      </c>
+      <c r="CH119" t="n">
+        <v>0.36287</v>
+      </c>
+      <c r="CI119" t="n">
+        <v>0.38357</v>
+      </c>
+      <c r="CJ119" t="n">
+        <v>0.36971</v>
+      </c>
+      <c r="CK119" t="n">
+        <v>0.2861</v>
+      </c>
+      <c r="CL119" t="n">
+        <v>0.2987</v>
+      </c>
+      <c r="CM119" t="n">
+        <v>0.3138</v>
+      </c>
+      <c r="CN119" t="n">
+        <v>0.30367</v>
+      </c>
+      <c r="CO119" t="n">
+        <v>0.3467</v>
+      </c>
+      <c r="CP119" t="n">
+        <v>0.3438</v>
+      </c>
+      <c r="CQ119" t="n">
+        <v>0.33736</v>
+      </c>
+      <c r="CR119" t="n">
+        <v>0.34989</v>
+      </c>
+      <c r="CS119" t="n">
+        <v>0.3434</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B120" t="n">
+        <v>0.32018</v>
+      </c>
+      <c r="C120" t="n">
+        <v>0.29226</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0.34724</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.31825</v>
+      </c>
+      <c r="F120" t="n">
+        <v>0.33128</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0.31927</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0.34505</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0.33436</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0.32704</v>
+      </c>
+      <c r="K120" t="n">
+        <v>0.3273</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0.30019</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0.30009</v>
+      </c>
+      <c r="N120" t="n">
+        <v>0.47042</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0.3115</v>
+      </c>
+      <c r="P120" t="n">
+        <v>0.31826</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>0.30019</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0.31598</v>
+      </c>
+      <c r="S120" t="n">
+        <v>0.31669</v>
+      </c>
+      <c r="T120" t="n">
+        <v>0.29557</v>
+      </c>
+      <c r="U120" t="n">
+        <v>0.29767</v>
+      </c>
+      <c r="V120" t="n">
+        <v>0.29453</v>
+      </c>
+      <c r="W120" t="n">
+        <v>0.2934</v>
+      </c>
+      <c r="X120" t="n">
+        <v>0.29495</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>0.33899</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>0.33923</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>0.36019</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>0.34079</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>0.39025</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>0.3177</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>0.32651</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>0.31014</v>
+      </c>
+      <c r="AG120" t="n">
+        <v>0.31759</v>
+      </c>
+      <c r="AH120" t="n">
+        <v>0.33844</v>
+      </c>
+      <c r="AI120" t="n">
+        <v>0.30555</v>
+      </c>
+      <c r="AJ120" t="n">
+        <v>0.28127</v>
+      </c>
+      <c r="AK120" t="n">
+        <v>0.26305</v>
+      </c>
+      <c r="AL120" t="n">
+        <v>0.20577</v>
+      </c>
+      <c r="AM120" t="n">
+        <v>0.12448</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>0.11798</v>
+      </c>
+      <c r="AO120" t="n">
+        <v>0.08749999999999999</v>
+      </c>
+      <c r="AP120" t="n">
+        <v>0.26523</v>
+      </c>
+      <c r="AQ120" t="n">
+        <v>0.22619</v>
+      </c>
+      <c r="AR120" t="n">
+        <v>0.11623</v>
+      </c>
+      <c r="AS120" t="n">
+        <v>0.2856</v>
+      </c>
+      <c r="AT120" t="n">
+        <v>0.4437</v>
+      </c>
+      <c r="AU120" t="n">
+        <v>0.28869</v>
+      </c>
+      <c r="AV120" t="n">
+        <v>0.37209</v>
+      </c>
+      <c r="AW120" t="n">
+        <v>0.19721</v>
+      </c>
+      <c r="AX120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ120" t="n">
+        <v>0.06412999999999999</v>
+      </c>
+      <c r="BA120" t="n">
+        <v>0.25687</v>
+      </c>
+      <c r="BB120" t="n">
+        <v>0.20468</v>
+      </c>
+      <c r="BC120" t="n">
+        <v>0.04178</v>
+      </c>
+      <c r="BD120" t="n">
+        <v>-0.02087</v>
+      </c>
+      <c r="BE120" t="n">
+        <v>0.26422</v>
+      </c>
+      <c r="BF120" t="n">
+        <v>-0.01033</v>
+      </c>
+      <c r="BG120" t="n">
+        <v>0.03265</v>
+      </c>
+      <c r="BH120" t="n">
+        <v>0.0624</v>
+      </c>
+      <c r="BI120" t="n">
+        <v>0.09812</v>
+      </c>
+      <c r="BJ120" t="n">
+        <v>0.35408</v>
+      </c>
+      <c r="BK120" t="n">
+        <v>0.31844</v>
+      </c>
+      <c r="BL120" t="n">
+        <v>0.25072</v>
+      </c>
+      <c r="BM120" t="n">
+        <v>0.19367</v>
+      </c>
+      <c r="BN120" t="n">
+        <v>0.2225</v>
+      </c>
+      <c r="BO120" t="n">
+        <v>0.18088</v>
+      </c>
+      <c r="BP120" t="n">
+        <v>0.23037</v>
+      </c>
+      <c r="BQ120" t="n">
+        <v>0.16109</v>
+      </c>
+      <c r="BR120" t="n">
+        <v>0.23471</v>
+      </c>
+      <c r="BS120" t="n">
+        <v>0.25118</v>
+      </c>
+      <c r="BT120" t="n">
+        <v>0.28954</v>
+      </c>
+      <c r="BU120" t="n">
+        <v>0.33439</v>
+      </c>
+      <c r="BV120" t="n">
+        <v>0.31193</v>
+      </c>
+      <c r="BW120" t="n">
+        <v>0.3368</v>
+      </c>
+      <c r="BX120" t="n">
+        <v>0.26432</v>
+      </c>
+      <c r="BY120" t="n">
+        <v>0.28202</v>
+      </c>
+      <c r="BZ120" t="n">
+        <v>0.29231</v>
+      </c>
+      <c r="CA120" t="n">
+        <v>0.41978</v>
+      </c>
+      <c r="CB120" t="n">
+        <v>0.48417</v>
+      </c>
+      <c r="CC120" t="n">
+        <v>0.40852</v>
+      </c>
+      <c r="CD120" t="n">
+        <v>0.39453</v>
+      </c>
+      <c r="CE120" t="n">
+        <v>0.32219</v>
+      </c>
+      <c r="CF120" t="n">
+        <v>0.31965</v>
+      </c>
+      <c r="CG120" t="n">
+        <v>0.32714</v>
+      </c>
+      <c r="CH120" t="n">
+        <v>0.33679</v>
+      </c>
+      <c r="CI120" t="n">
+        <v>0.30928</v>
+      </c>
+      <c r="CJ120" t="n">
+        <v>0.31191</v>
+      </c>
+      <c r="CK120" t="n">
+        <v>0.30677</v>
+      </c>
+      <c r="CL120" t="n">
+        <v>0.27728</v>
+      </c>
+      <c r="CM120" t="n">
+        <v>0.30696</v>
+      </c>
+      <c r="CN120" t="n">
+        <v>0.32054</v>
+      </c>
+      <c r="CO120" t="n">
+        <v>0.29422</v>
+      </c>
+      <c r="CP120" t="n">
+        <v>0.28998</v>
+      </c>
+      <c r="CQ120" t="n">
+        <v>0.29996</v>
+      </c>
+      <c r="CR120" t="n">
+        <v>0.28795</v>
+      </c>
+      <c r="CS120" t="n">
+        <v>0.29103</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B121" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="C121" t="n">
+        <v>0.29727</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0.34126</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0.36633</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0.34894</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0.33249</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0.30122</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0.31098</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0.30973</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0.30374</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0.30247</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0.28379</v>
+      </c>
+      <c r="N121" t="n">
+        <v>0.3041</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0.3012</v>
+      </c>
+      <c r="P121" t="n">
+        <v>0.28296</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>0.28644</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0.29018</v>
+      </c>
+      <c r="S121" t="n">
+        <v>0.29018</v>
+      </c>
+      <c r="T121" t="n">
+        <v>0.29023</v>
+      </c>
+      <c r="U121" t="n">
+        <v>0.29802</v>
+      </c>
+      <c r="V121" t="n">
+        <v>0.29214</v>
+      </c>
+      <c r="W121" t="n">
+        <v>0.29515</v>
+      </c>
+      <c r="X121" t="n">
+        <v>0.31235</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>0.30391</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>0.31648</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>0.32435</v>
+      </c>
+      <c r="AB121" t="n">
+        <v>0.32427</v>
+      </c>
+      <c r="AC121" t="n">
+        <v>0.33285</v>
+      </c>
+      <c r="AD121" t="n">
+        <v>0.32606</v>
+      </c>
+      <c r="AE121" t="n">
+        <v>0.27934</v>
+      </c>
+      <c r="AF121" t="n">
+        <v>0.26052</v>
+      </c>
+      <c r="AG121" t="n">
+        <v>0.04015999999999999</v>
+      </c>
+      <c r="AH121" t="n">
+        <v>0.04533</v>
+      </c>
+      <c r="AI121" t="n">
+        <v>0.03994</v>
+      </c>
+      <c r="AJ121" t="n">
+        <v>0.03979</v>
+      </c>
+      <c r="AK121" t="n">
+        <v>0.04296</v>
+      </c>
+      <c r="AL121" t="n">
+        <v>0.04616</v>
+      </c>
+      <c r="AM121" t="n">
+        <v>0.04453</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>0.04656</v>
+      </c>
+      <c r="AO121" t="n">
+        <v>-0.04204</v>
+      </c>
+      <c r="AP121" t="n">
+        <v>-0.04958</v>
+      </c>
+      <c r="AQ121" t="n">
+        <v>-0.04653</v>
+      </c>
+      <c r="AR121" t="n">
+        <v>-0.04614</v>
+      </c>
+      <c r="AS121" t="n">
+        <v>-0.04452</v>
+      </c>
+      <c r="AT121" t="n">
+        <v>-0.04466</v>
+      </c>
+      <c r="AU121" t="n">
+        <v>-0.04568</v>
+      </c>
+      <c r="AV121" t="n">
+        <v>-0.04461</v>
+      </c>
+      <c r="AW121" t="n">
+        <v>-0.04356</v>
+      </c>
+      <c r="AX121" t="n">
+        <v>-0.04596</v>
+      </c>
+      <c r="AY121" t="n">
+        <v>-0.04917</v>
+      </c>
+      <c r="AZ121" t="n">
+        <v>-0.04504</v>
+      </c>
+      <c r="BA121" t="n">
+        <v>-0.04576</v>
+      </c>
+      <c r="BB121" t="n">
+        <v>-0.04721</v>
+      </c>
+      <c r="BC121" t="n">
+        <v>-0.04711</v>
+      </c>
+      <c r="BD121" t="n">
+        <v>-0.04948</v>
+      </c>
+      <c r="BE121" t="n">
+        <v>-0.04503</v>
+      </c>
+      <c r="BF121" t="n">
+        <v>-0.04696</v>
+      </c>
+      <c r="BG121" t="n">
+        <v>0.22031</v>
+      </c>
+      <c r="BH121" t="n">
+        <v>0.04729</v>
+      </c>
+      <c r="BI121" t="n">
+        <v>0.05123</v>
+      </c>
+      <c r="BJ121" t="n">
+        <v>0.05342</v>
+      </c>
+      <c r="BK121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BM121" t="n">
+        <v>-0.00257</v>
+      </c>
+      <c r="BN121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BO121" t="n">
+        <v>0.14649</v>
+      </c>
+      <c r="BP121" t="n">
+        <v>0.0369</v>
+      </c>
+      <c r="BQ121" t="n">
+        <v>0.09844</v>
+      </c>
+      <c r="BR121" t="n">
+        <v>0.28968</v>
+      </c>
+      <c r="BS121" t="n">
+        <v>0.29185</v>
+      </c>
+      <c r="BT121" t="n">
+        <v>0.29303</v>
+      </c>
+      <c r="BU121" t="n">
+        <v>0.31984</v>
+      </c>
+      <c r="BV121" t="n">
+        <v>0.3294</v>
+      </c>
+      <c r="BW121" t="n">
+        <v>0.31427</v>
+      </c>
+      <c r="BX121" t="n">
+        <v>0.33492</v>
+      </c>
+      <c r="BY121" t="n">
+        <v>0.33006</v>
+      </c>
+      <c r="BZ121" t="n">
+        <v>0.33119</v>
+      </c>
+      <c r="CA121" t="n">
+        <v>0.32349</v>
+      </c>
+      <c r="CB121" t="n">
+        <v>0.3745</v>
+      </c>
+      <c r="CC121" t="n">
+        <v>0.388</v>
+      </c>
+      <c r="CD121" t="n">
+        <v>0.38286</v>
+      </c>
+      <c r="CE121" t="n">
+        <v>0.37785</v>
+      </c>
+      <c r="CF121" t="n">
+        <v>0.34128</v>
+      </c>
+      <c r="CG121" t="n">
+        <v>0.40072</v>
+      </c>
+      <c r="CH121" t="n">
+        <v>0.39715</v>
+      </c>
+      <c r="CI121" t="n">
+        <v>0.41202</v>
+      </c>
+      <c r="CJ121" t="n">
+        <v>0.46765</v>
+      </c>
+      <c r="CK121" t="n">
+        <v>0.35387</v>
+      </c>
+      <c r="CL121" t="n">
+        <v>0.39654</v>
+      </c>
+      <c r="CM121" t="n">
+        <v>0.40016</v>
+      </c>
+      <c r="CN121" t="n">
+        <v>0.4176</v>
+      </c>
+      <c r="CO121" t="n">
+        <v>0.35505</v>
+      </c>
+      <c r="CP121" t="n">
+        <v>0.35811</v>
+      </c>
+      <c r="CQ121" t="n">
+        <v>0.34528</v>
+      </c>
+      <c r="CR121" t="n">
+        <v>0.35518</v>
+      </c>
+      <c r="CS121" t="n">
+        <v>0.35139</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B122" t="n">
+        <v>0.36802</v>
+      </c>
+      <c r="C122" t="n">
+        <v>0.66361</v>
+      </c>
+      <c r="D122" t="n">
+        <v>0.40013</v>
+      </c>
+      <c r="E122" t="n">
+        <v>0.4466</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0.4238</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0.42388</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0.35995</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0.35938</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0.35911</v>
+      </c>
+      <c r="K122" t="n">
+        <v>0.33469</v>
+      </c>
+      <c r="L122" t="n">
+        <v>0.31032</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0.32568</v>
+      </c>
+      <c r="N122" t="n">
+        <v>0.35795</v>
+      </c>
+      <c r="O122" t="n">
+        <v>0.35662</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0.34869</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>0.34748</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0.33507</v>
+      </c>
+      <c r="S122" t="n">
+        <v>0.31551</v>
+      </c>
+      <c r="T122" t="n">
+        <v>0.33031</v>
+      </c>
+      <c r="U122" t="n">
+        <v>0.3356</v>
+      </c>
+      <c r="V122" t="n">
+        <v>0.32279</v>
+      </c>
+      <c r="W122" t="n">
+        <v>0.30015</v>
+      </c>
+      <c r="X122" t="n">
+        <v>0.32287</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>0.33542</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>0.33912</v>
+      </c>
+      <c r="AA122" t="n">
+        <v>0.35031</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>0.35212</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>0.34295</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>0.31619</v>
+      </c>
+      <c r="AE122" t="n">
+        <v>0.10251</v>
+      </c>
+      <c r="AF122" t="n">
+        <v>0.10242</v>
+      </c>
+      <c r="AG122" t="n">
+        <v>0.04247</v>
+      </c>
+      <c r="AH122" t="n">
+        <v>-0.04627000000000001</v>
+      </c>
+      <c r="AI122" t="n">
+        <v>-0.04577000000000001</v>
+      </c>
+      <c r="AJ122" t="n">
+        <v>-0.04532</v>
+      </c>
+      <c r="AK122" t="n">
+        <v>-0.04532</v>
+      </c>
+      <c r="AL122" t="n">
+        <v>-0.04532</v>
+      </c>
+      <c r="AM122" t="n">
+        <v>-0.04454</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>-0.04256</v>
+      </c>
+      <c r="AO122" t="n">
+        <v>-0.03196</v>
+      </c>
+      <c r="AP122" t="n">
+        <v>-0.04135</v>
+      </c>
+      <c r="AQ122" t="n">
+        <v>0.10655</v>
+      </c>
+      <c r="AR122" t="n">
+        <v>0.00045</v>
+      </c>
+      <c r="AS122" t="n">
+        <v>-0.03765</v>
+      </c>
+      <c r="AT122" t="n">
+        <v>-0.04706</v>
+      </c>
+      <c r="AU122" t="n">
+        <v>-0.04207</v>
+      </c>
+      <c r="AV122" t="n">
+        <v>-0.04217</v>
+      </c>
+      <c r="AW122" t="n">
+        <v>-0.04207</v>
+      </c>
+      <c r="AX122" t="n">
+        <v>-0.04437</v>
+      </c>
+      <c r="AY122" t="n">
+        <v>-0.04428</v>
+      </c>
+      <c r="AZ122" t="n">
+        <v>-0.04426</v>
+      </c>
+      <c r="BA122" t="n">
+        <v>-0.04203</v>
+      </c>
+      <c r="BB122" t="n">
+        <v>-0.04147</v>
+      </c>
+      <c r="BC122" t="n">
+        <v>-0.04398</v>
+      </c>
+      <c r="BD122" t="n">
+        <v>-0.04128</v>
+      </c>
+      <c r="BE122" t="n">
+        <v>-0.0398</v>
+      </c>
+      <c r="BF122" t="n">
+        <v>-0.04489</v>
+      </c>
+      <c r="BG122" t="n">
+        <v>-0.04399</v>
+      </c>
+      <c r="BH122" t="n">
+        <v>-0.04429</v>
+      </c>
+      <c r="BI122" t="n">
+        <v>-0.04183</v>
+      </c>
+      <c r="BJ122" t="n">
+        <v>-0.04286</v>
+      </c>
+      <c r="BK122" t="n">
+        <v>-0.04047</v>
+      </c>
+      <c r="BL122" t="n">
+        <v>-0.04295</v>
+      </c>
+      <c r="BM122" t="n">
+        <v>-0.0499</v>
+      </c>
+      <c r="BN122" t="n">
+        <v>-0.04374</v>
+      </c>
+      <c r="BO122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BP122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BQ122" t="n">
+        <v>-0.04683</v>
+      </c>
+      <c r="BR122" t="n">
+        <v>-0.04672</v>
+      </c>
+      <c r="BS122" t="n">
+        <v>0.2015</v>
+      </c>
+      <c r="BT122" t="n">
+        <v>0.14408</v>
+      </c>
+      <c r="BU122" t="n">
+        <v>0.29179</v>
+      </c>
+      <c r="BV122" t="n">
+        <v>0.29653</v>
+      </c>
+      <c r="BW122" t="n">
+        <v>0.30638</v>
+      </c>
+      <c r="BX122" t="n">
+        <v>0.30161</v>
+      </c>
+      <c r="BY122" t="n">
+        <v>0.29667</v>
+      </c>
+      <c r="BZ122" t="n">
+        <v>0.29405</v>
+      </c>
+      <c r="CA122" t="n">
+        <v>0.29526</v>
+      </c>
+      <c r="CB122" t="n">
+        <v>0.29432</v>
+      </c>
+      <c r="CC122" t="n">
+        <v>0.2988</v>
+      </c>
+      <c r="CD122" t="n">
+        <v>0.29249</v>
+      </c>
+      <c r="CE122" t="n">
+        <v>0.29652</v>
+      </c>
+      <c r="CF122" t="n">
+        <v>0.27049</v>
+      </c>
+      <c r="CG122" t="n">
+        <v>0.29546</v>
+      </c>
+      <c r="CH122" t="n">
+        <v>0.2996</v>
+      </c>
+      <c r="CI122" t="n">
+        <v>0.30958</v>
+      </c>
+      <c r="CJ122" t="n">
+        <v>0.30582</v>
+      </c>
+      <c r="CK122" t="n">
+        <v>0.30288</v>
+      </c>
+      <c r="CL122" t="n">
+        <v>0.31627</v>
+      </c>
+      <c r="CM122" t="n">
+        <v>0.32027</v>
+      </c>
+      <c r="CN122" t="n">
+        <v>0.34944</v>
+      </c>
+      <c r="CO122" t="n">
+        <v>0.35152</v>
+      </c>
+      <c r="CP122" t="n">
+        <v>0.34638</v>
+      </c>
+      <c r="CQ122" t="n">
+        <v>0.36843</v>
+      </c>
+      <c r="CR122" t="n">
+        <v>0.36689</v>
+      </c>
+      <c r="CS122" t="n">
+        <v>0.33702</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="B123" t="n">
+        <v>0.33208</v>
+      </c>
+      <c r="C123" t="n">
+        <v>1.32086</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0.31232</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0.4064700000000001</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0.35173</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0.32233</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0.30985</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0.31627</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0.30308</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0.28275</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0.29695</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0.29265</v>
+      </c>
+      <c r="N123" t="n">
+        <v>0.28973</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0.28279</v>
+      </c>
+      <c r="P123" t="n">
+        <v>0.27272</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>0.2727</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0.28257</v>
+      </c>
+      <c r="S123" t="n">
+        <v>0.17364</v>
+      </c>
+      <c r="T123" t="n">
+        <v>0.15989</v>
+      </c>
+      <c r="U123" t="n">
+        <v>0.17246</v>
+      </c>
+      <c r="V123" t="n">
+        <v>0.14895</v>
+      </c>
+      <c r="W123" t="n">
+        <v>0.16068</v>
+      </c>
+      <c r="X123" t="n">
+        <v>0.15998</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>0.23843</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>0.2154</v>
+      </c>
+      <c r="AA123" t="n">
+        <v>0.22795</v>
+      </c>
+      <c r="AB123" t="n">
+        <v>0.2711</v>
+      </c>
+      <c r="AC123" t="n">
+        <v>0.28756</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>0.29233</v>
+      </c>
+      <c r="AE123" t="n">
+        <v>0.32098</v>
+      </c>
+      <c r="AF123" t="n">
+        <v>0.29263</v>
+      </c>
+      <c r="AG123" t="n">
+        <v>0.28279</v>
+      </c>
+      <c r="AH123" t="n">
+        <v>0.28262</v>
+      </c>
+      <c r="AI123" t="n">
+        <v>0.28235</v>
+      </c>
+      <c r="AJ123" t="n">
+        <v>0.26944</v>
+      </c>
+      <c r="AK123" t="n">
+        <v>0.28238</v>
+      </c>
+      <c r="AL123" t="n">
+        <v>0.32442</v>
+      </c>
+      <c r="AM123" t="n">
+        <v>0.31215</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>0.30686</v>
+      </c>
+      <c r="AO123" t="n">
+        <v>0.31806</v>
+      </c>
+      <c r="AP123" t="n">
+        <v>0.31038</v>
+      </c>
+      <c r="AQ123" t="n">
+        <v>0.36012</v>
+      </c>
+      <c r="AR123" t="n">
+        <v>0.31338</v>
+      </c>
+      <c r="AS123" t="n">
+        <v>0.26794</v>
+      </c>
+      <c r="AT123" t="n">
+        <v>0.37531</v>
+      </c>
+      <c r="AU123" t="n">
+        <v>0.38124</v>
+      </c>
+      <c r="AV123" t="n">
+        <v>0.41787</v>
+      </c>
+      <c r="AW123" t="n">
+        <v>0.4254</v>
+      </c>
+      <c r="AX123" t="n">
+        <v>0.32927</v>
+      </c>
+      <c r="AY123" t="n">
+        <v>0.40718</v>
+      </c>
+      <c r="AZ123" t="n">
+        <v>0.40401</v>
+      </c>
+      <c r="BA123" t="n">
+        <v>0.38992</v>
+      </c>
+      <c r="BB123" t="n">
+        <v>0.39392</v>
+      </c>
+      <c r="BC123" t="n">
+        <v>0.29977</v>
+      </c>
+      <c r="BD123" t="n">
+        <v>0.30098</v>
+      </c>
+      <c r="BE123" t="n">
+        <v>0.29877</v>
+      </c>
+      <c r="BF123" t="n">
+        <v>0.30007</v>
+      </c>
+      <c r="BG123" t="n">
+        <v>0.15736</v>
+      </c>
+      <c r="BH123" t="n">
+        <v>0.28166</v>
+      </c>
+      <c r="BI123" t="n">
+        <v>0.30852</v>
+      </c>
+      <c r="BJ123" t="n">
+        <v>0.31095</v>
+      </c>
+      <c r="BK123" t="n">
+        <v>0.30587</v>
+      </c>
+      <c r="BL123" t="n">
+        <v>0.32189</v>
+      </c>
+      <c r="BM123" t="n">
+        <v>0.34107</v>
+      </c>
+      <c r="BN123" t="n">
+        <v>0.30044</v>
+      </c>
+      <c r="BO123" t="n">
+        <v>0.32988</v>
+      </c>
+      <c r="BP123" t="n">
+        <v>0.38117</v>
+      </c>
+      <c r="BQ123" t="n">
+        <v>0.47916</v>
+      </c>
+      <c r="BR123" t="n">
+        <v>0.50747</v>
+      </c>
+      <c r="BS123" t="n">
+        <v>0.79111</v>
+      </c>
+      <c r="BT123" t="n">
+        <v>0.6218899999999999</v>
+      </c>
+      <c r="BU123" t="n">
+        <v>0.78532</v>
+      </c>
+      <c r="BV123" t="n">
+        <v>0.39985</v>
+      </c>
+      <c r="BW123" t="n">
+        <v>0.49776</v>
+      </c>
+      <c r="BX123" t="n">
+        <v>0.78083</v>
+      </c>
+      <c r="BY123" t="n">
+        <v>0.91995</v>
+      </c>
+      <c r="BZ123" t="n">
+        <v>0.49424</v>
+      </c>
+      <c r="CA123" t="n">
+        <v>0.92331</v>
+      </c>
+      <c r="CB123" t="n">
+        <v>0.8929</v>
+      </c>
+      <c r="CC123" t="n">
+        <v>1.31155</v>
+      </c>
+      <c r="CD123" t="n">
+        <v>0.3823</v>
+      </c>
+      <c r="CE123" t="n">
+        <v>0.91587</v>
+      </c>
+      <c r="CF123" t="n">
+        <v>0.63625</v>
+      </c>
+      <c r="CG123" t="n">
+        <v>1.21492</v>
+      </c>
+      <c r="CH123" t="n">
+        <v>0.8824099999999999</v>
+      </c>
+      <c r="CI123" t="n">
+        <v>0.5661799999999999</v>
+      </c>
+      <c r="CJ123" t="n">
+        <v>1.35946</v>
+      </c>
+      <c r="CK123" t="n">
+        <v>1.05252</v>
+      </c>
+      <c r="CL123" t="n">
+        <v>0.55957</v>
+      </c>
+      <c r="CM123" t="n">
+        <v>0.81551</v>
+      </c>
+      <c r="CN123" t="n">
+        <v>0.53084</v>
+      </c>
+      <c r="CO123" t="n">
+        <v>0.79763</v>
+      </c>
+      <c r="CP123" t="n">
+        <v>0.7971</v>
+      </c>
+      <c r="CQ123" t="n">
+        <v>0.8797999999999999</v>
+      </c>
+      <c r="CR123" t="n">
+        <v>0.88675</v>
+      </c>
+      <c r="CS123" t="n">
+        <v>0.51619</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="B124" t="n">
+        <v>0.42115</v>
+      </c>
+      <c r="C124" t="n">
+        <v>1.42949</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0.47625</v>
+      </c>
+      <c r="E124" t="n">
+        <v>1.23659</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0.8796799999999999</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0.5515399999999999</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0.65118</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0.54564</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0.50613</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0.4594</v>
+      </c>
+      <c r="L124" t="n">
+        <v>0.42771</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0.44232</v>
+      </c>
+      <c r="N124" t="n">
+        <v>0.45133</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0.39559</v>
+      </c>
+      <c r="P124" t="n">
+        <v>0.45306</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>0.42152</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0.35564</v>
+      </c>
+      <c r="S124" t="n">
+        <v>0.4003</v>
+      </c>
+      <c r="T124" t="n">
+        <v>0.36552</v>
+      </c>
+      <c r="U124" t="n">
+        <v>0.39288</v>
+      </c>
+      <c r="V124" t="n">
+        <v>0.41517</v>
+      </c>
+      <c r="W124" t="n">
+        <v>0.4342200000000001</v>
+      </c>
+      <c r="X124" t="n">
+        <v>0.34421</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>0.39114</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>0.35083</v>
+      </c>
+      <c r="AA124" t="n">
+        <v>0.36398</v>
+      </c>
+      <c r="AB124" t="n">
+        <v>0.35982</v>
+      </c>
+      <c r="AC124" t="n">
+        <v>0.3607</v>
+      </c>
+      <c r="AD124" t="n">
+        <v>0.41019</v>
+      </c>
+      <c r="AE124" t="n">
+        <v>0.36228</v>
+      </c>
+      <c r="AF124" t="n">
+        <v>0.45114</v>
+      </c>
+      <c r="AG124" t="n">
+        <v>0.35777</v>
+      </c>
+      <c r="AH124" t="n">
+        <v>0.39987</v>
+      </c>
+      <c r="AI124" t="n">
+        <v>0.40058</v>
+      </c>
+      <c r="AJ124" t="n">
+        <v>0.58872</v>
+      </c>
+      <c r="AK124" t="n">
+        <v>0.42842</v>
+      </c>
+      <c r="AL124" t="n">
+        <v>0.59662</v>
+      </c>
+      <c r="AM124" t="n">
+        <v>0.60157</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>0.6556000000000001</v>
+      </c>
+      <c r="AO124" t="n">
+        <v>0.45171</v>
+      </c>
+      <c r="AP124" t="n">
+        <v>0.40525</v>
+      </c>
+      <c r="AQ124" t="n">
+        <v>0.55559</v>
+      </c>
+      <c r="AR124" t="n">
+        <v>0.44642</v>
+      </c>
+      <c r="AS124" t="n">
+        <v>0.86205</v>
+      </c>
+      <c r="AT124" t="n">
+        <v>0.66104</v>
+      </c>
+      <c r="AU124" t="n">
+        <v>0.82909</v>
+      </c>
+      <c r="AV124" t="n">
+        <v>0.81211</v>
+      </c>
+      <c r="AW124" t="n">
+        <v>0.84735</v>
+      </c>
+      <c r="AX124" t="n">
+        <v>0.3251</v>
+      </c>
+      <c r="AY124" t="n">
+        <v>0.43256</v>
+      </c>
+      <c r="AZ124" t="n">
+        <v>0.32891</v>
+      </c>
+      <c r="BA124" t="n">
+        <v>0.32474</v>
+      </c>
+      <c r="BB124" t="n">
+        <v>0.30199</v>
+      </c>
+      <c r="BC124" t="n">
+        <v>0.28156</v>
+      </c>
+      <c r="BD124" t="n">
+        <v>0.41835</v>
+      </c>
+      <c r="BE124" t="n">
+        <v>0.29352</v>
+      </c>
+      <c r="BF124" t="n">
+        <v>0.27122</v>
+      </c>
+      <c r="BG124" t="n">
+        <v>0.30655</v>
+      </c>
+      <c r="BH124" t="n">
+        <v>0.35836</v>
+      </c>
+      <c r="BI124" t="n">
+        <v>0.33245</v>
+      </c>
+      <c r="BJ124" t="n">
+        <v>0.31958</v>
+      </c>
+      <c r="BK124" t="n">
+        <v>0.33924</v>
+      </c>
+      <c r="BL124" t="n">
+        <v>0.33981</v>
+      </c>
+      <c r="BM124" t="n">
+        <v>0.31777</v>
+      </c>
+      <c r="BN124" t="n">
+        <v>0.30623</v>
+      </c>
+      <c r="BO124" t="n">
+        <v>0.31908</v>
+      </c>
+      <c r="BP124" t="n">
+        <v>0.31975</v>
+      </c>
+      <c r="BQ124" t="n">
+        <v>0.34431</v>
+      </c>
+      <c r="BR124" t="n">
+        <v>0.31475</v>
+      </c>
+      <c r="BS124" t="n">
+        <v>0.31488</v>
+      </c>
+      <c r="BT124" t="n">
+        <v>0.32069</v>
+      </c>
+      <c r="BU124" t="n">
+        <v>0.31628</v>
+      </c>
+      <c r="BV124" t="n">
+        <v>0.32747</v>
+      </c>
+      <c r="BW124" t="n">
+        <v>0.31239</v>
+      </c>
+      <c r="BX124" t="n">
+        <v>0.31389</v>
+      </c>
+      <c r="BY124" t="n">
+        <v>0.3125</v>
+      </c>
+      <c r="BZ124" t="n">
+        <v>0.3152799999999999</v>
+      </c>
+      <c r="CA124" t="n">
+        <v>0.30986</v>
+      </c>
+      <c r="CB124" t="n">
+        <v>0.31642</v>
+      </c>
+      <c r="CC124" t="n">
+        <v>0.32306</v>
+      </c>
+      <c r="CD124" t="n">
+        <v>0.32456</v>
+      </c>
+      <c r="CE124" t="n">
+        <v>0.32635</v>
+      </c>
+      <c r="CF124" t="n">
+        <v>0.35554</v>
+      </c>
+      <c r="CG124" t="n">
+        <v>0.34198</v>
+      </c>
+      <c r="CH124" t="n">
+        <v>0.34017</v>
+      </c>
+      <c r="CI124" t="n">
+        <v>0.33892</v>
+      </c>
+      <c r="CJ124" t="n">
+        <v>0.33063</v>
+      </c>
+      <c r="CK124" t="n">
+        <v>0.33744</v>
+      </c>
+      <c r="CL124" t="n">
+        <v>0.33556</v>
+      </c>
+      <c r="CM124" t="n">
+        <v>0.41033</v>
+      </c>
+      <c r="CN124" t="n">
+        <v>0.41304</v>
+      </c>
+      <c r="CO124" t="n">
+        <v>0.45288</v>
+      </c>
+      <c r="CP124" t="n">
+        <v>0.4154</v>
+      </c>
+      <c r="CQ124" t="n">
+        <v>0.39184</v>
+      </c>
+      <c r="CR124" t="n">
+        <v>0.37529</v>
+      </c>
+      <c r="CS124" t="n">
+        <v>0.35338</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B125" t="n">
+        <v>0.33004</v>
+      </c>
+      <c r="C125" t="n">
+        <v>0.98819</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0.36084</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0.48775</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0.45241</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0.54688</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0.61513</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0.40327</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0.41003</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0.41909</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0.46043</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0.41388</v>
+      </c>
+      <c r="N125" t="n">
+        <v>0.35931</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0.38838</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0.33085</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>0.35951</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0.3460299999999999</v>
+      </c>
+      <c r="S125" t="n">
+        <v>0.32326</v>
+      </c>
+      <c r="T125" t="n">
+        <v>0.40052</v>
+      </c>
+      <c r="U125" t="n">
+        <v>0.50073</v>
+      </c>
+      <c r="V125" t="n">
+        <v>0.35747</v>
+      </c>
+      <c r="W125" t="n">
+        <v>0.388</v>
+      </c>
+      <c r="X125" t="n">
+        <v>0.34379</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>0.35116</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>0.35554</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>0.37085</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>0.35769</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>0.36283</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>0.31625</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>0.31335</v>
+      </c>
+      <c r="AF125" t="n">
+        <v>0.33237</v>
+      </c>
+      <c r="AG125" t="n">
+        <v>0.33793</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>0.33795</v>
+      </c>
+      <c r="AI125" t="n">
+        <v>0.34948</v>
+      </c>
+      <c r="AJ125" t="n">
+        <v>0.31536</v>
+      </c>
+      <c r="AK125" t="n">
+        <v>0.3026</v>
+      </c>
+      <c r="AL125" t="n">
+        <v>0.29047</v>
+      </c>
+      <c r="AM125" t="n">
+        <v>0.30336</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>0.28893</v>
+      </c>
+      <c r="AO125" t="n">
+        <v>0.27779</v>
+      </c>
+      <c r="AP125" t="n">
+        <v>0.16457</v>
+      </c>
+      <c r="AQ125" t="n">
+        <v>0.28123</v>
+      </c>
+      <c r="AR125" t="n">
+        <v>0.30788</v>
+      </c>
+      <c r="AS125" t="n">
+        <v>0.32953</v>
+      </c>
+      <c r="AT125" t="n">
+        <v>0.30374</v>
+      </c>
+      <c r="AU125" t="n">
+        <v>0.31176</v>
+      </c>
+      <c r="AV125" t="n">
+        <v>0.29681</v>
+      </c>
+      <c r="AW125" t="n">
+        <v>0.26084</v>
+      </c>
+      <c r="AX125" t="n">
+        <v>0.20056</v>
+      </c>
+      <c r="AY125" t="n">
+        <v>0.2775</v>
+      </c>
+      <c r="AZ125" t="n">
+        <v>0.25742</v>
+      </c>
+      <c r="BA125" t="n">
+        <v>0.34836</v>
+      </c>
+      <c r="BB125" t="n">
+        <v>0.27501</v>
+      </c>
+      <c r="BC125" t="n">
+        <v>0.31276</v>
+      </c>
+      <c r="BD125" t="n">
+        <v>0.31879</v>
+      </c>
+      <c r="BE125" t="n">
+        <v>0.34134</v>
+      </c>
+      <c r="BF125" t="n">
+        <v>0.35875</v>
+      </c>
+      <c r="BG125" t="n">
+        <v>0.32088</v>
+      </c>
+      <c r="BH125" t="n">
+        <v>0.31253</v>
+      </c>
+      <c r="BI125" t="n">
+        <v>0.31984</v>
+      </c>
+      <c r="BJ125" t="n">
+        <v>0.30506</v>
+      </c>
+      <c r="BK125" t="n">
+        <v>0.31301</v>
+      </c>
+      <c r="BL125" t="n">
+        <v>0.28982</v>
+      </c>
+      <c r="BM125" t="n">
+        <v>0.30225</v>
+      </c>
+      <c r="BN125" t="n">
+        <v>0.29113</v>
+      </c>
+      <c r="BO125" t="n">
+        <v>0.30916</v>
+      </c>
+      <c r="BP125" t="n">
+        <v>0.32046</v>
+      </c>
+      <c r="BQ125" t="n">
+        <v>0.31159</v>
+      </c>
+      <c r="BR125" t="n">
+        <v>0.28987</v>
+      </c>
+      <c r="BS125" t="n">
+        <v>0.34749</v>
+      </c>
+      <c r="BT125" t="n">
+        <v>0.2554</v>
+      </c>
+      <c r="BU125" t="n">
+        <v>0.35021</v>
+      </c>
+      <c r="BV125" t="n">
+        <v>0.32215</v>
+      </c>
+      <c r="BW125" t="n">
+        <v>0.2688</v>
+      </c>
+      <c r="BX125" t="n">
+        <v>0.35242</v>
+      </c>
+      <c r="BY125" t="n">
+        <v>0.27544</v>
+      </c>
+      <c r="BZ125" t="n">
+        <v>0.34932</v>
+      </c>
+      <c r="CA125" t="n">
+        <v>0.32885</v>
+      </c>
+      <c r="CB125" t="n">
+        <v>0.33848</v>
+      </c>
+      <c r="CC125" t="n">
+        <v>0.31006</v>
+      </c>
+      <c r="CD125" t="n">
+        <v>0.34938</v>
+      </c>
+      <c r="CE125" t="n">
+        <v>0.31634</v>
+      </c>
+      <c r="CF125" t="n">
+        <v>0.38541</v>
+      </c>
+      <c r="CG125" t="n">
+        <v>0.32274</v>
+      </c>
+      <c r="CH125" t="n">
+        <v>0.43183</v>
+      </c>
+      <c r="CI125" t="n">
+        <v>0.35004</v>
+      </c>
+      <c r="CJ125" t="n">
+        <v>0.27648</v>
+      </c>
+      <c r="CK125" t="n">
+        <v>0.42323</v>
+      </c>
+      <c r="CL125" t="n">
+        <v>0.35059</v>
+      </c>
+      <c r="CM125" t="n">
+        <v>0.44774</v>
+      </c>
+      <c r="CN125" t="n">
+        <v>0.31778</v>
+      </c>
+      <c r="CO125" t="n">
+        <v>0.42076</v>
+      </c>
+      <c r="CP125" t="n">
+        <v>0.35908</v>
+      </c>
+      <c r="CQ125" t="n">
+        <v>0.40207</v>
+      </c>
+      <c r="CR125" t="n">
+        <v>0.40081</v>
+      </c>
+      <c r="CS125" t="n">
+        <v>0.59782</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B126" t="n">
+        <v>0.35053</v>
+      </c>
+      <c r="C126" t="n">
+        <v>0.88967</v>
+      </c>
+      <c r="D126" t="n">
+        <v>1.35074</v>
+      </c>
+      <c r="E126" t="n">
+        <v>1.14036</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0.7074600000000001</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0.80025</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0.65228</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0.58775</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0.4512</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0.45042</v>
+      </c>
+      <c r="L126" t="n">
+        <v>0.50054</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0.43997</v>
+      </c>
+      <c r="N126" t="n">
+        <v>0.43773</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0.41512</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0.41299</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0.42377</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0.5010899999999999</v>
+      </c>
+      <c r="S126" t="n">
+        <v>0.41299</v>
+      </c>
+      <c r="T126" t="n">
+        <v>0.43414</v>
+      </c>
+      <c r="U126" t="n">
+        <v>0.41328</v>
+      </c>
+      <c r="V126" t="n">
+        <v>0.43418</v>
+      </c>
+      <c r="W126" t="n">
+        <v>0.39047</v>
+      </c>
+      <c r="X126" t="n">
+        <v>0.42845</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>0.4509</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>0.39638</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>0.42356</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>0.43455</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>0.41299</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>0.41296</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>0.40061</v>
+      </c>
+      <c r="AF126" t="n">
+        <v>0.42398</v>
+      </c>
+      <c r="AG126" t="n">
+        <v>0.39636</v>
+      </c>
+      <c r="AH126" t="n">
+        <v>0.40282</v>
+      </c>
+      <c r="AI126" t="n">
+        <v>0.56186</v>
+      </c>
+      <c r="AJ126" t="n">
+        <v>0.37337</v>
+      </c>
+      <c r="AK126" t="n">
+        <v>0.35544</v>
+      </c>
+      <c r="AL126" t="n">
+        <v>0.29738</v>
+      </c>
+      <c r="AM126" t="n">
+        <v>0.36938</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>0.36254</v>
+      </c>
+      <c r="AO126" t="n">
+        <v>0.30088</v>
+      </c>
+      <c r="AP126" t="n">
+        <v>0.33236</v>
+      </c>
+      <c r="AQ126" t="n">
+        <v>0.30047</v>
+      </c>
+      <c r="AR126" t="n">
+        <v>0.31858</v>
+      </c>
+      <c r="AS126" t="n">
+        <v>0.30996</v>
+      </c>
+      <c r="AT126" t="n">
+        <v>0.06581999999999999</v>
+      </c>
+      <c r="AU126" t="n">
+        <v>0.55199</v>
+      </c>
+      <c r="AV126" t="n">
+        <v>0.36474</v>
+      </c>
+      <c r="AW126" t="n">
+        <v>0.32327</v>
+      </c>
+      <c r="AX126" t="n">
+        <v>0.24994</v>
+      </c>
+      <c r="AY126" t="n">
+        <v>-0.04063</v>
+      </c>
+      <c r="AZ126" t="n">
+        <v>0.6716599999999999</v>
+      </c>
+      <c r="BA126" t="n">
+        <v>0.21941</v>
+      </c>
+      <c r="BB126" t="n">
+        <v>0.32791</v>
+      </c>
+      <c r="BC126" t="n">
+        <v>0.31106</v>
+      </c>
+      <c r="BD126" t="n">
+        <v>0.35513</v>
+      </c>
+      <c r="BE126" t="n">
+        <v>0.54799</v>
+      </c>
+      <c r="BF126" t="n">
+        <v>0.3041</v>
+      </c>
+      <c r="BG126" t="n">
+        <v>0.26572</v>
+      </c>
+      <c r="BH126" t="n">
+        <v>0.26575</v>
+      </c>
+      <c r="BI126" t="n">
+        <v>0.29714</v>
+      </c>
+      <c r="BJ126" t="n">
+        <v>0.26574</v>
+      </c>
+      <c r="BK126" t="n">
+        <v>0.28936</v>
+      </c>
+      <c r="BL126" t="n">
+        <v>0.38342</v>
+      </c>
+      <c r="BM126" t="n">
+        <v>0.2944</v>
+      </c>
+      <c r="BN126" t="n">
+        <v>0.34234</v>
+      </c>
+      <c r="BO126" t="n">
+        <v>0.29452</v>
+      </c>
+      <c r="BP126" t="n">
+        <v>0.30812</v>
+      </c>
+      <c r="BQ126" t="n">
+        <v>0.31946</v>
+      </c>
+      <c r="BR126" t="n">
+        <v>0.31437</v>
+      </c>
+      <c r="BS126" t="n">
+        <v>0.34011</v>
+      </c>
+      <c r="BT126" t="n">
+        <v>0.33833</v>
+      </c>
+      <c r="BU126" t="n">
+        <v>0.38575</v>
+      </c>
+      <c r="BV126" t="n">
+        <v>0.40003</v>
+      </c>
+      <c r="BW126" t="n">
+        <v>0.34683</v>
+      </c>
+      <c r="BX126" t="n">
+        <v>0.35925</v>
+      </c>
+      <c r="BY126" t="n">
+        <v>0.33961</v>
+      </c>
+      <c r="BZ126" t="n">
+        <v>0.33532</v>
+      </c>
+      <c r="CA126" t="n">
+        <v>0.37257</v>
+      </c>
+      <c r="CB126" t="n">
+        <v>0.43898</v>
+      </c>
+      <c r="CC126" t="n">
+        <v>0.35995</v>
+      </c>
+      <c r="CD126" t="n">
+        <v>0.40648</v>
+      </c>
+      <c r="CE126" t="n">
+        <v>0.36408</v>
+      </c>
+      <c r="CF126" t="n">
+        <v>0.35247</v>
+      </c>
+      <c r="CG126" t="n">
+        <v>0.587</v>
+      </c>
+      <c r="CH126" t="n">
+        <v>0.46451</v>
+      </c>
+      <c r="CI126" t="n">
+        <v>0.71458</v>
+      </c>
+      <c r="CJ126" t="n">
+        <v>0.46584</v>
+      </c>
+      <c r="CK126" t="n">
+        <v>0.43871</v>
+      </c>
+      <c r="CL126" t="n">
+        <v>0.37615</v>
+      </c>
+      <c r="CM126" t="n">
+        <v>0.42465</v>
+      </c>
+      <c r="CN126" t="n">
+        <v>0.38743</v>
+      </c>
+      <c r="CO126" t="n">
+        <v>0.37052</v>
+      </c>
+      <c r="CP126" t="n">
+        <v>0.33546</v>
+      </c>
+      <c r="CQ126" t="n">
+        <v>0.34176</v>
+      </c>
+      <c r="CR126" t="n">
+        <v>0.33039</v>
+      </c>
+      <c r="CS126" t="n">
+        <v>0.32572</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B127" t="n">
+        <v>0.31946</v>
+      </c>
+      <c r="C127" t="n">
+        <v>0.42473</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0.34055</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0.3454100000000001</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0.34139</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0.3369</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0.32748</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0.33073</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0.32753</v>
+      </c>
+      <c r="K127" t="n">
+        <v>0.32621</v>
+      </c>
+      <c r="L127" t="n">
+        <v>0.32554</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0.3112</v>
+      </c>
+      <c r="N127" t="n">
+        <v>0.32843</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0.32726</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0.32088</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>0.31693</v>
+      </c>
+      <c r="R127" t="n">
+        <v>0.32139</v>
+      </c>
+      <c r="S127" t="n">
+        <v>0.32137</v>
+      </c>
+      <c r="T127" t="n">
+        <v>0.31097</v>
+      </c>
+      <c r="U127" t="n">
+        <v>0.32588</v>
+      </c>
+      <c r="V127" t="n">
+        <v>0.31194</v>
+      </c>
+      <c r="W127" t="n">
+        <v>0.32111</v>
+      </c>
+      <c r="X127" t="n">
+        <v>0.32164</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>0.39298</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>0.32701</v>
+      </c>
+      <c r="AA127" t="n">
+        <v>0.35107</v>
+      </c>
+      <c r="AB127" t="n">
+        <v>0.40147</v>
+      </c>
+      <c r="AC127" t="n">
+        <v>0.37632</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>0.35084</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>0.3396</v>
+      </c>
+      <c r="AF127" t="n">
+        <v>0.35599</v>
+      </c>
+      <c r="AG127" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="AH127" t="n">
+        <v>0.33421</v>
+      </c>
+      <c r="AI127" t="n">
+        <v>0.31902</v>
+      </c>
+      <c r="AJ127" t="n">
+        <v>0.26003</v>
+      </c>
+      <c r="AK127" t="n">
+        <v>0.33221</v>
+      </c>
+      <c r="AL127" t="n">
+        <v>0.32081</v>
+      </c>
+      <c r="AM127" t="n">
+        <v>0.26842</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>0.30537</v>
+      </c>
+      <c r="AO127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP127" t="n">
+        <v>0.29207</v>
+      </c>
+      <c r="AQ127" t="n">
+        <v>0.23588</v>
+      </c>
+      <c r="AR127" t="n">
+        <v>0.145</v>
+      </c>
+      <c r="AS127" t="n">
+        <v>0.14732</v>
+      </c>
+      <c r="AT127" t="n">
+        <v>0.29647</v>
+      </c>
+      <c r="AU127" t="n">
+        <v>0.15418</v>
+      </c>
+      <c r="AV127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX127" t="n">
+        <v>0.14439</v>
+      </c>
+      <c r="AY127" t="n">
+        <v>0.14084</v>
+      </c>
+      <c r="AZ127" t="n">
+        <v>0.14418</v>
+      </c>
+      <c r="BA127" t="n">
+        <v>0.14265</v>
+      </c>
+      <c r="BB127" t="n">
+        <v>0.25745</v>
+      </c>
+      <c r="BC127" t="n">
+        <v>0.14472</v>
+      </c>
+      <c r="BD127" t="n">
+        <v>0.26679</v>
+      </c>
+      <c r="BE127" t="n">
+        <v>0.26717</v>
+      </c>
+      <c r="BF127" t="n">
+        <v>0.14218</v>
+      </c>
+      <c r="BG127" t="n">
+        <v>0.03487</v>
+      </c>
+      <c r="BH127" t="n">
+        <v>0.11417</v>
+      </c>
+      <c r="BI127" t="n">
+        <v>0.11328</v>
+      </c>
+      <c r="BJ127" t="n">
+        <v>0.14545</v>
+      </c>
+      <c r="BK127" t="n">
+        <v>0.14152</v>
+      </c>
+      <c r="BL127" t="n">
+        <v>0.1467</v>
+      </c>
+      <c r="BM127" t="n">
+        <v>0.28742</v>
+      </c>
+      <c r="BN127" t="n">
+        <v>0.32395</v>
+      </c>
+      <c r="BO127" t="n">
+        <v>0.33039</v>
+      </c>
+      <c r="BP127" t="n">
+        <v>0.32195</v>
+      </c>
+      <c r="BQ127" t="n">
+        <v>0.34584</v>
+      </c>
+      <c r="BR127" t="n">
+        <v>0.31669</v>
+      </c>
+      <c r="BS127" t="n">
+        <v>0.35624</v>
+      </c>
+      <c r="BT127" t="n">
+        <v>0.34912</v>
+      </c>
+      <c r="BU127" t="n">
+        <v>0.38086</v>
+      </c>
+      <c r="BV127" t="n">
+        <v>0.34407</v>
+      </c>
+      <c r="BW127" t="n">
+        <v>0.38064</v>
+      </c>
+      <c r="BX127" t="n">
+        <v>0.34673</v>
+      </c>
+      <c r="BY127" t="n">
+        <v>0.3991</v>
+      </c>
+      <c r="BZ127" t="n">
+        <v>0.36136</v>
+      </c>
+      <c r="CA127" t="n">
+        <v>0.38567</v>
+      </c>
+      <c r="CB127" t="n">
+        <v>0.45084</v>
+      </c>
+      <c r="CC127" t="n">
+        <v>0.4007</v>
+      </c>
+      <c r="CD127" t="n">
+        <v>0.39324</v>
+      </c>
+      <c r="CE127" t="n">
+        <v>0.40291</v>
+      </c>
+      <c r="CF127" t="n">
+        <v>0.39879</v>
+      </c>
+      <c r="CG127" t="n">
+        <v>0.44092</v>
+      </c>
+      <c r="CH127" t="n">
+        <v>0.44108</v>
+      </c>
+      <c r="CI127" t="n">
+        <v>0.44047</v>
+      </c>
+      <c r="CJ127" t="n">
+        <v>0.44541</v>
+      </c>
+      <c r="CK127" t="n">
+        <v>0.44487</v>
+      </c>
+      <c r="CL127" t="n">
+        <v>0.40349</v>
+      </c>
+      <c r="CM127" t="n">
+        <v>0.39124</v>
+      </c>
+      <c r="CN127" t="n">
+        <v>0.39842</v>
+      </c>
+      <c r="CO127" t="n">
+        <v>0.39219</v>
+      </c>
+      <c r="CP127" t="n">
+        <v>0.36055</v>
+      </c>
+      <c r="CQ127" t="n">
+        <v>0.36125</v>
+      </c>
+      <c r="CR127" t="n">
+        <v>0.34892</v>
+      </c>
+      <c r="CS127" t="n">
+        <v>0.3501</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B128" t="n">
+        <v>0.34043</v>
+      </c>
+      <c r="C128" t="n">
+        <v>0.5515</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0.38974</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0.46977</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0.42481</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0.41685</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0.37048</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0.38195</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0.38121</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0.39399</v>
+      </c>
+      <c r="L128" t="n">
+        <v>0.38069</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0.37016</v>
+      </c>
+      <c r="N128" t="n">
+        <v>0.38067</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0.36042</v>
+      </c>
+      <c r="P128" t="n">
+        <v>0.39155</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>0.37062</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0.38072</v>
+      </c>
+      <c r="S128" t="n">
+        <v>0.35056</v>
+      </c>
+      <c r="T128" t="n">
+        <v>0.34756</v>
+      </c>
+      <c r="U128" t="n">
+        <v>0.35556</v>
+      </c>
+      <c r="V128" t="n">
+        <v>0.34517</v>
+      </c>
+      <c r="W128" t="n">
+        <v>0.34049</v>
+      </c>
+      <c r="X128" t="n">
+        <v>0.34551</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>0.3405</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>0.34512</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>0.35585</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>0.3706</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>0.38043</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>0.36019</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>0.34019</v>
+      </c>
+      <c r="AF128" t="n">
+        <v>0.34048</v>
+      </c>
+      <c r="AG128" t="n">
+        <v>0.34048</v>
+      </c>
+      <c r="AH128" t="n">
+        <v>0.33154</v>
+      </c>
+      <c r="AI128" t="n">
+        <v>0.3467</v>
+      </c>
+      <c r="AJ128" t="n">
+        <v>0.35642</v>
+      </c>
+      <c r="AK128" t="n">
+        <v>0.40334</v>
+      </c>
+      <c r="AL128" t="n">
+        <v>0.26884</v>
+      </c>
+      <c r="AM128" t="n">
+        <v>0.3093</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>0.30905</v>
+      </c>
+      <c r="AO128" t="n">
+        <v>0.30269</v>
+      </c>
+      <c r="AP128" t="n">
+        <v>0.26482</v>
+      </c>
+      <c r="AQ128" t="n">
+        <v>0.27328</v>
+      </c>
+      <c r="AR128" t="n">
+        <v>0.23894</v>
+      </c>
+      <c r="AS128" t="n">
+        <v>0.23443</v>
+      </c>
+      <c r="AT128" t="n">
+        <v>0.18216</v>
+      </c>
+      <c r="AU128" t="n">
+        <v>0.27562</v>
+      </c>
+      <c r="AV128" t="n">
+        <v>0.23845</v>
+      </c>
+      <c r="AW128" t="n">
+        <v>0.21646</v>
+      </c>
+      <c r="AX128" t="n">
+        <v>0.2412</v>
+      </c>
+      <c r="AY128" t="n">
+        <v>0.2907</v>
+      </c>
+      <c r="AZ128" t="n">
+        <v>0.27256</v>
+      </c>
+      <c r="BA128" t="n">
+        <v>0.30828</v>
+      </c>
+      <c r="BB128" t="n">
+        <v>0.26263</v>
+      </c>
+      <c r="BC128" t="n">
+        <v>0.28558</v>
+      </c>
+      <c r="BD128" t="n">
+        <v>0.28905</v>
+      </c>
+      <c r="BE128" t="n">
+        <v>0.28049</v>
+      </c>
+      <c r="BF128" t="n">
+        <v>0.2825299999999999</v>
+      </c>
+      <c r="BG128" t="n">
+        <v>0.27013</v>
+      </c>
+      <c r="BH128" t="n">
+        <v>0.21652</v>
+      </c>
+      <c r="BI128" t="n">
+        <v>0.30268</v>
+      </c>
+      <c r="BJ128" t="n">
+        <v>0.27539</v>
+      </c>
+      <c r="BK128" t="n">
+        <v>0.29679</v>
+      </c>
+      <c r="BL128" t="n">
+        <v>0.27336</v>
+      </c>
+      <c r="BM128" t="n">
+        <v>0.25783</v>
+      </c>
+      <c r="BN128" t="n">
+        <v>0.31402</v>
+      </c>
+      <c r="BO128" t="n">
+        <v>0.33643</v>
+      </c>
+      <c r="BP128" t="n">
+        <v>0.34119</v>
+      </c>
+      <c r="BQ128" t="n">
+        <v>0.32648</v>
+      </c>
+      <c r="BR128" t="n">
+        <v>0.32021</v>
+      </c>
+      <c r="BS128" t="n">
+        <v>0.30698</v>
+      </c>
+      <c r="BT128" t="n">
+        <v>0.32065</v>
+      </c>
+      <c r="BU128" t="n">
+        <v>0.33028</v>
+      </c>
+      <c r="BV128" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="BW128" t="n">
+        <v>0.34785</v>
+      </c>
+      <c r="BX128" t="n">
+        <v>0.36441</v>
+      </c>
+      <c r="BY128" t="n">
+        <v>0.36484</v>
+      </c>
+      <c r="BZ128" t="n">
+        <v>0.37847</v>
+      </c>
+      <c r="CA128" t="n">
+        <v>0.41376</v>
+      </c>
+      <c r="CB128" t="n">
+        <v>0.4211</v>
+      </c>
+      <c r="CC128" t="n">
+        <v>0.24395</v>
+      </c>
+      <c r="CD128" t="n">
+        <v>0.39502</v>
+      </c>
+      <c r="CE128" t="n">
+        <v>0.38245</v>
+      </c>
+      <c r="CF128" t="n">
+        <v>0.35459</v>
+      </c>
+      <c r="CG128" t="n">
+        <v>0.35718</v>
+      </c>
+      <c r="CH128" t="n">
+        <v>0.35485</v>
+      </c>
+      <c r="CI128" t="n">
+        <v>0.41809</v>
+      </c>
+      <c r="CJ128" t="n">
+        <v>0.44744</v>
+      </c>
+      <c r="CK128" t="n">
+        <v>0.34819</v>
+      </c>
+      <c r="CL128" t="n">
+        <v>0.36755</v>
+      </c>
+      <c r="CM128" t="n">
+        <v>0.37049</v>
+      </c>
+      <c r="CN128" t="n">
+        <v>0.36042</v>
+      </c>
+      <c r="CO128" t="n">
+        <v>0.38074</v>
+      </c>
+      <c r="CP128" t="n">
+        <v>0.38053</v>
+      </c>
+      <c r="CQ128" t="n">
+        <v>0.38568</v>
+      </c>
+      <c r="CR128" t="n">
+        <v>0.35039</v>
+      </c>
+      <c r="CS128" t="n">
+        <v>0.36055</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B129" t="n">
+        <v>0.3403</v>
+      </c>
+      <c r="C129" t="n">
+        <v>0.36644</v>
+      </c>
+      <c r="D129" t="n">
+        <v>0.42003</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0.37081</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0.39196</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0.38098</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0.35298</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0.34977</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0.36058</v>
+      </c>
+      <c r="K129" t="n">
+        <v>0.35196</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0.34221</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0.34797</v>
+      </c>
+      <c r="N129" t="n">
+        <v>0.34597</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0.34999</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0.34731</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>0.35001</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0.34087</v>
+      </c>
+      <c r="S129" t="n">
+        <v>0.34241</v>
+      </c>
+      <c r="T129" t="n">
+        <v>0.3434</v>
+      </c>
+      <c r="U129" t="n">
+        <v>0.33878</v>
+      </c>
+      <c r="V129" t="n">
+        <v>0.33855</v>
+      </c>
+      <c r="W129" t="n">
+        <v>0.34027</v>
+      </c>
+      <c r="X129" t="n">
+        <v>0.33082</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>0.34139</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>0.3325</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>0.35053</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>0.34451</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>0.36173</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>0.31316</v>
+      </c>
+      <c r="AE129" t="n">
+        <v>0.32903</v>
+      </c>
+      <c r="AF129" t="n">
+        <v>0.33945</v>
+      </c>
+      <c r="AG129" t="n">
+        <v>0.32576</v>
+      </c>
+      <c r="AH129" t="n">
+        <v>0.31821</v>
+      </c>
+      <c r="AI129" t="n">
+        <v>0.33137</v>
+      </c>
+      <c r="AJ129" t="n">
+        <v>0.32019</v>
+      </c>
+      <c r="AK129" t="n">
+        <v>0.30935</v>
+      </c>
+      <c r="AL129" t="n">
+        <v>0.35263</v>
+      </c>
+      <c r="AM129" t="n">
+        <v>0.33146</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>0.2807</v>
+      </c>
+      <c r="AO129" t="n">
+        <v>0.36951</v>
+      </c>
+      <c r="AP129" t="n">
+        <v>0.40709</v>
+      </c>
+      <c r="AQ129" t="n">
+        <v>0.2958</v>
+      </c>
+      <c r="AR129" t="n">
+        <v>0.38963</v>
+      </c>
+      <c r="AS129" t="n">
+        <v>0.27381</v>
+      </c>
+      <c r="AT129" t="n">
+        <v>0.26545</v>
+      </c>
+      <c r="AU129" t="n">
+        <v>0.33433</v>
+      </c>
+      <c r="AV129" t="n">
+        <v>-0.03965</v>
+      </c>
+      <c r="AW129" t="n">
+        <v>0.24947</v>
+      </c>
+      <c r="AX129" t="n">
+        <v>0.24995</v>
+      </c>
+      <c r="AY129" t="n">
+        <v>0.19611</v>
+      </c>
+      <c r="AZ129" t="n">
+        <v>0.0703</v>
+      </c>
+      <c r="BA129" t="n">
+        <v>0.17785</v>
+      </c>
+      <c r="BB129" t="n">
+        <v>0.2441</v>
+      </c>
+      <c r="BC129" t="n">
+        <v>0.28462</v>
+      </c>
+      <c r="BD129" t="n">
+        <v>0.31124</v>
+      </c>
+      <c r="BE129" t="n">
+        <v>0.26665</v>
+      </c>
+      <c r="BF129" t="n">
+        <v>0.24849</v>
+      </c>
+      <c r="BG129" t="n">
+        <v>0.28473</v>
+      </c>
+      <c r="BH129" t="n">
+        <v>0.29838</v>
+      </c>
+      <c r="BI129" t="n">
+        <v>0.29284</v>
+      </c>
+      <c r="BJ129" t="n">
+        <v>0.26781</v>
+      </c>
+      <c r="BK129" t="n">
+        <v>0.29324</v>
+      </c>
+      <c r="BL129" t="n">
+        <v>0.32686</v>
+      </c>
+      <c r="BM129" t="n">
+        <v>0.32288</v>
+      </c>
+      <c r="BN129" t="n">
+        <v>0.32129</v>
+      </c>
+      <c r="BO129" t="n">
+        <v>0.40981</v>
+      </c>
+      <c r="BP129" t="n">
+        <v>0.33164</v>
+      </c>
+      <c r="BQ129" t="n">
+        <v>0.32488</v>
+      </c>
+      <c r="BR129" t="n">
+        <v>0.33297</v>
+      </c>
+      <c r="BS129" t="n">
+        <v>0.34214</v>
+      </c>
+      <c r="BT129" t="n">
+        <v>0.30236</v>
+      </c>
+      <c r="BU129" t="n">
+        <v>0.37655</v>
+      </c>
+      <c r="BV129" t="n">
+        <v>0.30944</v>
+      </c>
+      <c r="BW129" t="n">
+        <v>0.31368</v>
+      </c>
+      <c r="BX129" t="n">
+        <v>0.31857</v>
+      </c>
+      <c r="BY129" t="n">
+        <v>0.32816</v>
+      </c>
+      <c r="BZ129" t="n">
+        <v>0.32014</v>
+      </c>
+      <c r="CA129" t="n">
+        <v>0.46985</v>
+      </c>
+      <c r="CB129" t="n">
+        <v>0.40298</v>
+      </c>
+      <c r="CC129" t="n">
+        <v>0.73164</v>
+      </c>
+      <c r="CD129" t="n">
+        <v>0.35217</v>
+      </c>
+      <c r="CE129" t="n">
+        <v>0.40798</v>
+      </c>
+      <c r="CF129" t="n">
+        <v>0.34626</v>
+      </c>
+      <c r="CG129" t="n">
+        <v>0.33058</v>
+      </c>
+      <c r="CH129" t="n">
+        <v>0.33884</v>
+      </c>
+      <c r="CI129" t="n">
+        <v>0.45142</v>
+      </c>
+      <c r="CJ129" t="n">
+        <v>0.35417</v>
+      </c>
+      <c r="CK129" t="n">
+        <v>0.40493</v>
+      </c>
+      <c r="CL129" t="n">
+        <v>0.29884</v>
+      </c>
+      <c r="CM129" t="n">
+        <v>0.34269</v>
+      </c>
+      <c r="CN129" t="n">
+        <v>0.34516</v>
+      </c>
+      <c r="CO129" t="n">
+        <v>0.34581</v>
+      </c>
+      <c r="CP129" t="n">
+        <v>0.31734</v>
+      </c>
+      <c r="CQ129" t="n">
+        <v>0.31098</v>
+      </c>
+      <c r="CR129" t="n">
+        <v>0.31818</v>
+      </c>
+      <c r="CS129" t="n">
+        <v>0.30113</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="B130" t="n">
+        <v>0.33787</v>
+      </c>
+      <c r="C130" t="n">
+        <v>0.30495</v>
+      </c>
+      <c r="D130" t="n">
+        <v>0.34129</v>
+      </c>
+      <c r="E130" t="n">
+        <v>0.33117</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0.32848</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0.3254</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0.33036</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0.32527</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0.32556</v>
+      </c>
+      <c r="K130" t="n">
+        <v>0.32478</v>
+      </c>
+      <c r="L130" t="n">
+        <v>0.32398</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0.32659</v>
+      </c>
+      <c r="N130" t="n">
+        <v>0.32458</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0.32748</v>
+      </c>
+      <c r="P130" t="n">
+        <v>0.32878</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>0.32734</v>
+      </c>
+      <c r="R130" t="n">
+        <v>0.32768</v>
+      </c>
+      <c r="S130" t="n">
+        <v>0.32421</v>
+      </c>
+      <c r="T130" t="n">
+        <v>0.33132</v>
+      </c>
+      <c r="U130" t="n">
+        <v>0.32648</v>
+      </c>
+      <c r="V130" t="n">
+        <v>0.32113</v>
+      </c>
+      <c r="W130" t="n">
+        <v>0.31981</v>
+      </c>
+      <c r="X130" t="n">
+        <v>0.32311</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>0.32652</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>0.33113</v>
+      </c>
+      <c r="AA130" t="n">
+        <v>0.33546</v>
+      </c>
+      <c r="AB130" t="n">
+        <v>0.34657</v>
+      </c>
+      <c r="AC130" t="n">
+        <v>0.3411</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>0.34119</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>0.33572</v>
+      </c>
+      <c r="AF130" t="n">
+        <v>0.33908</v>
+      </c>
+      <c r="AG130" t="n">
+        <v>0.32155</v>
+      </c>
+      <c r="AH130" t="n">
+        <v>0.3213</v>
+      </c>
+      <c r="AI130" t="n">
+        <v>0.33447</v>
+      </c>
+      <c r="AJ130" t="n">
+        <v>0.34985</v>
+      </c>
+      <c r="AK130" t="n">
+        <v>0.35431</v>
+      </c>
+      <c r="AL130" t="n">
+        <v>0.33435</v>
+      </c>
+      <c r="AM130" t="n">
+        <v>0.32429</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>0.31841</v>
+      </c>
+      <c r="AO130" t="n">
+        <v>0.31619</v>
+      </c>
+      <c r="AP130" t="n">
+        <v>0.32338</v>
+      </c>
+      <c r="AQ130" t="n">
+        <v>0.31597</v>
+      </c>
+      <c r="AR130" t="n">
+        <v>0.33733</v>
+      </c>
+      <c r="AS130" t="n">
+        <v>0.27888</v>
+      </c>
+      <c r="AT130" t="n">
+        <v>0.34192</v>
+      </c>
+      <c r="AU130" t="n">
+        <v>0.34077</v>
+      </c>
+      <c r="AV130" t="n">
+        <v>0.29011</v>
+      </c>
+      <c r="AW130" t="n">
+        <v>0.32581</v>
+      </c>
+      <c r="AX130" t="n">
+        <v>0.28182</v>
+      </c>
+      <c r="AY130" t="n">
+        <v>0.32481</v>
+      </c>
+      <c r="AZ130" t="n">
+        <v>0.31866</v>
+      </c>
+      <c r="BA130" t="n">
+        <v>0.3197</v>
+      </c>
+      <c r="BB130" t="n">
+        <v>0.32568</v>
+      </c>
+      <c r="BC130" t="n">
+        <v>0.32867</v>
+      </c>
+      <c r="BD130" t="n">
+        <v>0.33327</v>
+      </c>
+      <c r="BE130" t="n">
+        <v>0.331</v>
+      </c>
+      <c r="BF130" t="n">
+        <v>0.31335</v>
+      </c>
+      <c r="BG130" t="n">
+        <v>0.32669</v>
+      </c>
+      <c r="BH130" t="n">
+        <v>0.31954</v>
+      </c>
+      <c r="BI130" t="n">
+        <v>0.32011</v>
+      </c>
+      <c r="BJ130" t="n">
+        <v>0.31996</v>
+      </c>
+      <c r="BK130" t="n">
+        <v>0.3135</v>
+      </c>
+      <c r="BL130" t="n">
+        <v>0.34911</v>
+      </c>
+      <c r="BM130" t="n">
+        <v>0.30327</v>
+      </c>
+      <c r="BN130" t="n">
+        <v>0.28382</v>
+      </c>
+      <c r="BO130" t="n">
+        <v>0.31426</v>
+      </c>
+      <c r="BP130" t="n">
+        <v>0.34327</v>
+      </c>
+      <c r="BQ130" t="n">
+        <v>0.32288</v>
+      </c>
+      <c r="BR130" t="n">
+        <v>0.34067</v>
+      </c>
+      <c r="BS130" t="n">
+        <v>0.3315</v>
+      </c>
+      <c r="BT130" t="n">
+        <v>0.35012</v>
+      </c>
+      <c r="BU130" t="n">
+        <v>0.35016</v>
+      </c>
+      <c r="BV130" t="n">
+        <v>0.35017</v>
+      </c>
+      <c r="BW130" t="n">
+        <v>0.36014</v>
+      </c>
+      <c r="BX130" t="n">
+        <v>0.32637</v>
+      </c>
+      <c r="BY130" t="n">
+        <v>0.32951</v>
+      </c>
+      <c r="BZ130" t="n">
+        <v>0.34775</v>
+      </c>
+      <c r="CA130" t="n">
+        <v>0.37824</v>
+      </c>
+      <c r="CB130" t="n">
+        <v>0.36926</v>
+      </c>
+      <c r="CC130" t="n">
+        <v>0.36378</v>
+      </c>
+      <c r="CD130" t="n">
+        <v>0.3702</v>
+      </c>
+      <c r="CE130" t="n">
+        <v>0.36461</v>
+      </c>
+      <c r="CF130" t="n">
+        <v>0.37542</v>
+      </c>
+      <c r="CG130" t="n">
+        <v>0.36292</v>
+      </c>
+      <c r="CH130" t="n">
+        <v>0.3965</v>
+      </c>
+      <c r="CI130" t="n">
+        <v>0.38576</v>
+      </c>
+      <c r="CJ130" t="n">
+        <v>0.37168</v>
+      </c>
+      <c r="CK130" t="n">
+        <v>0.4045</v>
+      </c>
+      <c r="CL130" t="n">
+        <v>0.35505</v>
+      </c>
+      <c r="CM130" t="n">
+        <v>0.38068</v>
+      </c>
+      <c r="CN130" t="n">
+        <v>0.3718399999999999</v>
+      </c>
+      <c r="CO130" t="n">
+        <v>0.36127</v>
+      </c>
+      <c r="CP130" t="n">
+        <v>0.35062</v>
+      </c>
+      <c r="CQ130" t="n">
+        <v>0.3501</v>
+      </c>
+      <c r="CR130" t="n">
+        <v>0.34995</v>
+      </c>
+      <c r="CS130" t="n">
+        <v>0.34925</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B131" t="n">
+        <v>0.3399</v>
+      </c>
+      <c r="C131" t="n">
+        <v>0.35195</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0.35759</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0.35707</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0.35174</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0.3509</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0.3501</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0.34988</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0.34975</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0.34658</v>
+      </c>
+      <c r="L131" t="n">
+        <v>0.36093</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0.34739</v>
+      </c>
+      <c r="N131" t="n">
+        <v>0.3507</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0.34992</v>
+      </c>
+      <c r="P131" t="n">
+        <v>0.33716</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>0.33988</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0.3401</v>
+      </c>
+      <c r="S131" t="n">
+        <v>0.33996</v>
+      </c>
+      <c r="T131" t="n">
+        <v>0.36995</v>
+      </c>
+      <c r="U131" t="n">
+        <v>0.32444</v>
+      </c>
+      <c r="V131" t="n">
+        <v>0.33865</v>
+      </c>
+      <c r="W131" t="n">
+        <v>0.33988</v>
+      </c>
+      <c r="X131" t="n">
+        <v>0.34992</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>0.33698</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="AA131" t="n">
+        <v>0.3451</v>
+      </c>
+      <c r="AB131" t="n">
+        <v>0.3362</v>
+      </c>
+      <c r="AC131" t="n">
+        <v>0.3499</v>
+      </c>
+      <c r="AD131" t="n">
+        <v>0.3499</v>
+      </c>
+      <c r="AE131" t="n">
+        <v>0.3366</v>
+      </c>
+      <c r="AF131" t="n">
+        <v>0.34022</v>
+      </c>
+      <c r="AG131" t="n">
+        <v>0.32828</v>
+      </c>
+      <c r="AH131" t="n">
+        <v>0.34895</v>
+      </c>
+      <c r="AI131" t="n">
+        <v>0.33997</v>
+      </c>
+      <c r="AJ131" t="n">
+        <v>0.33177</v>
+      </c>
+      <c r="AK131" t="n">
+        <v>0.33629</v>
+      </c>
+      <c r="AL131" t="n">
+        <v>0.28195</v>
+      </c>
+      <c r="AM131" t="n">
+        <v>0.32635</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>0.32769</v>
+      </c>
+      <c r="AO131" t="n">
+        <v>0.32868</v>
+      </c>
+      <c r="AP131" t="n">
+        <v>0.32544</v>
+      </c>
+      <c r="AQ131" t="n">
+        <v>0.31842</v>
+      </c>
+      <c r="AR131" t="n">
+        <v>0.32738</v>
+      </c>
+      <c r="AS131" t="n">
+        <v>0.31841</v>
+      </c>
+      <c r="AT131" t="n">
+        <v>0.31852</v>
+      </c>
+      <c r="AU131" t="n">
+        <v>0.32868</v>
+      </c>
+      <c r="AV131" t="n">
+        <v>0.32502</v>
+      </c>
+      <c r="AW131" t="n">
+        <v>0.32882</v>
+      </c>
+      <c r="AX131" t="n">
+        <v>0.31907</v>
+      </c>
+      <c r="AY131" t="n">
+        <v>0.37089</v>
+      </c>
+      <c r="AZ131" t="n">
+        <v>0.3244</v>
+      </c>
+      <c r="BA131" t="n">
+        <v>0.32041</v>
+      </c>
+      <c r="BB131" t="n">
+        <v>0.31786</v>
+      </c>
+      <c r="BC131" t="n">
+        <v>0.31538</v>
+      </c>
+      <c r="BD131" t="n">
+        <v>0.32381</v>
+      </c>
+      <c r="BE131" t="n">
+        <v>0.32183</v>
+      </c>
+      <c r="BF131" t="n">
+        <v>0.32727</v>
+      </c>
+      <c r="BG131" t="n">
+        <v>0.3213</v>
+      </c>
+      <c r="BH131" t="n">
+        <v>0.32291</v>
+      </c>
+      <c r="BI131" t="n">
+        <v>0.32968</v>
+      </c>
+      <c r="BJ131" t="n">
+        <v>0.33018</v>
+      </c>
+      <c r="BK131" t="n">
+        <v>0.33173</v>
+      </c>
+      <c r="BL131" t="n">
+        <v>0.33607</v>
+      </c>
+      <c r="BM131" t="n">
+        <v>0.34572</v>
+      </c>
+      <c r="BN131" t="n">
+        <v>0.3585</v>
+      </c>
+      <c r="BO131" t="n">
+        <v>0.6039500000000001</v>
+      </c>
+      <c r="BP131" t="n">
+        <v>0.39528</v>
+      </c>
+      <c r="BQ131" t="n">
+        <v>0.35476</v>
+      </c>
+      <c r="BR131" t="n">
+        <v>0.35524</v>
+      </c>
+      <c r="BS131" t="n">
+        <v>0.36665</v>
+      </c>
+      <c r="BT131" t="n">
+        <v>0.35067</v>
+      </c>
+      <c r="BU131" t="n">
+        <v>0.36025</v>
+      </c>
+      <c r="BV131" t="n">
+        <v>0.34748</v>
+      </c>
+      <c r="BW131" t="n">
+        <v>0.36059</v>
+      </c>
+      <c r="BX131" t="n">
+        <v>0.36051</v>
+      </c>
+      <c r="BY131" t="n">
+        <v>0.36254</v>
+      </c>
+      <c r="BZ131" t="n">
+        <v>0.35049</v>
+      </c>
+      <c r="CA131" t="n">
+        <v>0.37923</v>
+      </c>
+      <c r="CB131" t="n">
+        <v>0.38046</v>
+      </c>
+      <c r="CC131" t="n">
+        <v>0.38165</v>
+      </c>
+      <c r="CD131" t="n">
+        <v>0.38339</v>
+      </c>
+      <c r="CE131" t="n">
+        <v>0.42962</v>
+      </c>
+      <c r="CF131" t="n">
+        <v>0.40829</v>
+      </c>
+      <c r="CG131" t="n">
+        <v>0.38697</v>
+      </c>
+      <c r="CH131" t="n">
+        <v>0.38658</v>
+      </c>
+      <c r="CI131" t="n">
+        <v>0.64766</v>
+      </c>
+      <c r="CJ131" t="n">
+        <v>0.83441</v>
+      </c>
+      <c r="CK131" t="n">
+        <v>0.47448</v>
+      </c>
+      <c r="CL131" t="n">
+        <v>0.42112</v>
+      </c>
+      <c r="CM131" t="n">
+        <v>0.45851</v>
+      </c>
+      <c r="CN131" t="n">
+        <v>0.39311</v>
+      </c>
+      <c r="CO131" t="n">
+        <v>0.35095</v>
+      </c>
+      <c r="CP131" t="n">
+        <v>0.35084</v>
+      </c>
+      <c r="CQ131" t="n">
+        <v>0.35991</v>
+      </c>
+      <c r="CR131" t="n">
+        <v>0.3400899999999999</v>
+      </c>
+      <c r="CS131" t="n">
+        <v>0.34504</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="B132" t="n">
+        <v>0.31727</v>
+      </c>
+      <c r="C132" t="n">
+        <v>0.41085</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0.37632</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0.37154</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0.36339</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0.35992</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0.35978</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0.36286</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0.35956</v>
+      </c>
+      <c r="K132" t="n">
+        <v>0.36099</v>
+      </c>
+      <c r="L132" t="n">
+        <v>0.35984</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0.35375</v>
+      </c>
+      <c r="N132" t="n">
+        <v>0.36079</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0.36096</v>
+      </c>
+      <c r="P132" t="n">
+        <v>0.35705</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>0.35245</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0.35993</v>
+      </c>
+      <c r="S132" t="n">
+        <v>0.36026</v>
+      </c>
+      <c r="T132" t="n">
+        <v>0.35991</v>
+      </c>
+      <c r="U132" t="n">
+        <v>0.34366</v>
+      </c>
+      <c r="V132" t="n">
+        <v>0.37105</v>
+      </c>
+      <c r="W132" t="n">
+        <v>0.35883</v>
+      </c>
+      <c r="X132" t="n">
+        <v>0.35655</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>0.36013</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>0.36013</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>0.37971</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>0.3659</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>0.37979</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>0.35657</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>0.35653</v>
+      </c>
+      <c r="AF132" t="n">
+        <v>0.35117</v>
+      </c>
+      <c r="AG132" t="n">
+        <v>0.35186</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>0.35846</v>
+      </c>
+      <c r="AI132" t="n">
+        <v>0.34999</v>
+      </c>
+      <c r="AJ132" t="n">
+        <v>0.33001</v>
+      </c>
+      <c r="AK132" t="n">
+        <v>0.31991</v>
+      </c>
+      <c r="AL132" t="n">
+        <v>0.33138</v>
+      </c>
+      <c r="AM132" t="n">
+        <v>0.32141</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>0.26056</v>
+      </c>
+      <c r="AO132" t="n">
+        <v>0.13356</v>
+      </c>
+      <c r="AP132" t="n">
+        <v>0.28924</v>
+      </c>
+      <c r="AQ132" t="n">
+        <v>0.28392</v>
+      </c>
+      <c r="AR132" t="n">
+        <v>0.2824</v>
+      </c>
+      <c r="AS132" t="n">
+        <v>0.19456</v>
+      </c>
+      <c r="AT132" t="n">
+        <v>0.24432</v>
+      </c>
+      <c r="AU132" t="n">
+        <v>0.27829</v>
+      </c>
+      <c r="AV132" t="n">
+        <v>-0.02274</v>
+      </c>
+      <c r="AW132" t="n">
+        <v>0.27955</v>
+      </c>
+      <c r="AX132" t="n">
+        <v>0.11495</v>
+      </c>
+      <c r="AY132" t="n">
+        <v>-0.02323</v>
+      </c>
+      <c r="AZ132" t="n">
+        <v>0.28389</v>
+      </c>
+      <c r="BA132" t="n">
+        <v>0.23061</v>
+      </c>
+      <c r="BB132" t="n">
+        <v>0.28697</v>
+      </c>
+      <c r="BC132" t="n">
+        <v>0.24039</v>
+      </c>
+      <c r="BD132" t="n">
+        <v>0.30284</v>
+      </c>
+      <c r="BE132" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BF132" t="n">
+        <v>0.30231</v>
+      </c>
+      <c r="BG132" t="n">
+        <v>0.14382</v>
+      </c>
+      <c r="BH132" t="n">
+        <v>0.29619</v>
+      </c>
+      <c r="BI132" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ132" t="n">
+        <v>0.20882</v>
+      </c>
+      <c r="BK132" t="n">
+        <v>0.21649</v>
+      </c>
+      <c r="BL132" t="n">
+        <v>0.28308</v>
+      </c>
+      <c r="BM132" t="n">
+        <v>0.28552</v>
+      </c>
+      <c r="BN132" t="n">
+        <v>0.29587</v>
+      </c>
+      <c r="BO132" t="n">
+        <v>0.29343</v>
+      </c>
+      <c r="BP132" t="n">
+        <v>0.30149</v>
+      </c>
+      <c r="BQ132" t="n">
+        <v>0.28969</v>
+      </c>
+      <c r="BR132" t="n">
+        <v>0.30881</v>
+      </c>
+      <c r="BS132" t="n">
+        <v>0.33167</v>
+      </c>
+      <c r="BT132" t="n">
+        <v>0.33888</v>
+      </c>
+      <c r="BU132" t="n">
+        <v>0.33738</v>
+      </c>
+      <c r="BV132" t="n">
+        <v>0.29435</v>
+      </c>
+      <c r="BW132" t="n">
+        <v>0.33936</v>
+      </c>
+      <c r="BX132" t="n">
+        <v>0.41487</v>
+      </c>
+      <c r="BY132" t="n">
+        <v>0.36528</v>
+      </c>
+      <c r="BZ132" t="n">
+        <v>0.40534</v>
+      </c>
+      <c r="CA132" t="n">
+        <v>0.64854</v>
+      </c>
+      <c r="CB132" t="n">
+        <v>0.61342</v>
+      </c>
+      <c r="CC132" t="n">
+        <v>0.60785</v>
+      </c>
+      <c r="CD132" t="n">
+        <v>0.46504</v>
+      </c>
+      <c r="CE132" t="n">
+        <v>0.62881</v>
+      </c>
+      <c r="CF132" t="n">
+        <v>0.47371</v>
+      </c>
+      <c r="CG132" t="n">
+        <v>0.74314</v>
+      </c>
+      <c r="CH132" t="n">
+        <v>0.44686</v>
+      </c>
+      <c r="CI132" t="n">
+        <v>0.45764</v>
+      </c>
+      <c r="CJ132" t="n">
+        <v>0.40063</v>
+      </c>
+      <c r="CK132" t="n">
+        <v>0.37621</v>
+      </c>
+      <c r="CL132" t="n">
+        <v>0.35555</v>
+      </c>
+      <c r="CM132" t="n">
+        <v>0.47811</v>
+      </c>
+      <c r="CN132" t="n">
+        <v>0.42958</v>
+      </c>
+      <c r="CO132" t="n">
+        <v>0.41898</v>
+      </c>
+      <c r="CP132" t="n">
+        <v>0.37868</v>
+      </c>
+      <c r="CQ132" t="n">
+        <v>0.37477</v>
+      </c>
+      <c r="CR132" t="n">
+        <v>0.36735</v>
+      </c>
+      <c r="CS132" t="n">
+        <v>0.36023</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B133" t="n">
+        <v>0.34587</v>
+      </c>
+      <c r="C133" t="n">
+        <v>0.48961</v>
+      </c>
+      <c r="D133" t="n">
+        <v>0.46201</v>
+      </c>
+      <c r="E133" t="n">
+        <v>0.4605</v>
+      </c>
+      <c r="F133" t="n">
+        <v>0.44937</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0.4194</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0.39957</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0.40564</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0.41233</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0.40992</v>
+      </c>
+      <c r="L133" t="n">
+        <v>0.41812</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0.40063</v>
+      </c>
+      <c r="N133" t="n">
+        <v>0.39687</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0.41246</v>
+      </c>
+      <c r="P133" t="n">
+        <v>0.41006</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>0.39407</v>
+      </c>
+      <c r="R133" t="n">
+        <v>0.38792</v>
+      </c>
+      <c r="S133" t="n">
+        <v>0.41848</v>
+      </c>
+      <c r="T133" t="n">
+        <v>0.38808</v>
+      </c>
+      <c r="U133" t="n">
+        <v>0.41663</v>
+      </c>
+      <c r="V133" t="n">
+        <v>0.39029</v>
+      </c>
+      <c r="W133" t="n">
+        <v>0.40008</v>
+      </c>
+      <c r="X133" t="n">
+        <v>0.40002</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>0.41257</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>0.39993</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>0.44976</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>0.44881</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>0.5584600000000001</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>0.49907</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>0.44991</v>
+      </c>
+      <c r="AF133" t="n">
+        <v>0.36595</v>
+      </c>
+      <c r="AG133" t="n">
+        <v>0.4141</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>0.3648</v>
+      </c>
+      <c r="AI133" t="n">
+        <v>0.32201</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>0.36801</v>
+      </c>
+      <c r="AK133" t="n">
+        <v>0.37339</v>
+      </c>
+      <c r="AL133" t="n">
+        <v>0.42681</v>
+      </c>
+      <c r="AM133" t="n">
+        <v>0.363</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>0.38883</v>
+      </c>
+      <c r="AO133" t="n">
+        <v>0.32241</v>
+      </c>
+      <c r="AP133" t="n">
+        <v>0.28719</v>
+      </c>
+      <c r="AQ133" t="n">
+        <v>0.31493</v>
+      </c>
+      <c r="AR133" t="n">
+        <v>0.33602</v>
+      </c>
+      <c r="AS133" t="n">
+        <v>0.36831</v>
+      </c>
+      <c r="AT133" t="n">
+        <v>0.35717</v>
+      </c>
+      <c r="AU133" t="n">
+        <v>0.37198</v>
+      </c>
+      <c r="AV133" t="n">
+        <v>0.28709</v>
+      </c>
+      <c r="AW133" t="n">
+        <v>0.23872</v>
+      </c>
+      <c r="AX133" t="n">
+        <v>0.26377</v>
+      </c>
+      <c r="AY133" t="n">
+        <v>0.1245</v>
+      </c>
+      <c r="AZ133" t="n">
+        <v>-0.00512</v>
+      </c>
+      <c r="BA133" t="n">
+        <v>-0.01519</v>
+      </c>
+      <c r="BB133" t="n">
+        <v>0.29533</v>
+      </c>
+      <c r="BC133" t="n">
+        <v>0.29808</v>
+      </c>
+      <c r="BD133" t="n">
+        <v>0.67264</v>
+      </c>
+      <c r="BE133" t="n">
+        <v>0.34777</v>
+      </c>
+      <c r="BF133" t="n">
+        <v>0.26381</v>
+      </c>
+      <c r="BG133" t="n">
+        <v>0.11634</v>
+      </c>
+      <c r="BH133" t="n">
+        <v>0.08070000000000001</v>
+      </c>
+      <c r="BI133" t="n">
+        <v>-0.04813</v>
+      </c>
+      <c r="BJ133" t="n">
+        <v>0.25335</v>
+      </c>
+      <c r="BK133" t="n">
+        <v>-0.01091</v>
+      </c>
+      <c r="BL133" t="n">
+        <v>0.32752</v>
+      </c>
+      <c r="BM133" t="n">
+        <v>0.32414</v>
+      </c>
+      <c r="BN133" t="n">
+        <v>0.31323</v>
+      </c>
+      <c r="BO133" t="n">
+        <v>0.32652</v>
+      </c>
+      <c r="BP133" t="n">
+        <v>0.34734</v>
+      </c>
+      <c r="BQ133" t="n">
+        <v>0.32751</v>
+      </c>
+      <c r="BR133" t="n">
+        <v>0.33843</v>
+      </c>
+      <c r="BS133" t="n">
+        <v>0.33106</v>
+      </c>
+      <c r="BT133" t="n">
+        <v>0.33961</v>
+      </c>
+      <c r="BU133" t="n">
+        <v>0.33627</v>
+      </c>
+      <c r="BV133" t="n">
+        <v>0.32356</v>
+      </c>
+      <c r="BW133" t="n">
+        <v>0.35091</v>
+      </c>
+      <c r="BX133" t="n">
+        <v>0.41269</v>
+      </c>
+      <c r="BY133" t="n">
+        <v>0.48331</v>
+      </c>
+      <c r="BZ133" t="n">
+        <v>0.42683</v>
+      </c>
+      <c r="CA133" t="n">
+        <v>0.50589</v>
+      </c>
+      <c r="CB133" t="n">
+        <v>0.5075</v>
+      </c>
+      <c r="CC133" t="n">
+        <v>0.40508</v>
+      </c>
+      <c r="CD133" t="n">
+        <v>0.57292</v>
+      </c>
+      <c r="CE133" t="n">
+        <v>0.68591</v>
+      </c>
+      <c r="CF133" t="n">
+        <v>0.67196</v>
+      </c>
+      <c r="CG133" t="n">
+        <v>0.65808</v>
+      </c>
+      <c r="CH133" t="n">
+        <v>0.75049</v>
+      </c>
+      <c r="CI133" t="n">
+        <v>0.53625</v>
+      </c>
+      <c r="CJ133" t="n">
+        <v>0.52203</v>
+      </c>
+      <c r="CK133" t="n">
+        <v>0.8166</v>
+      </c>
+      <c r="CL133" t="n">
+        <v>0.75229</v>
+      </c>
+      <c r="CM133" t="n">
+        <v>0.60423</v>
+      </c>
+      <c r="CN133" t="n">
+        <v>0.65344</v>
+      </c>
+      <c r="CO133" t="n">
+        <v>0.41073</v>
+      </c>
+      <c r="CP133" t="n">
+        <v>0.43997</v>
+      </c>
+      <c r="CQ133" t="n">
+        <v>0.48128</v>
+      </c>
+      <c r="CR133" t="n">
+        <v>0.47798</v>
+      </c>
+      <c r="CS133" t="n">
+        <v>0.47189</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B134" t="n">
+        <v>0.41914</v>
+      </c>
+      <c r="C134" t="n">
+        <v>0.53235</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0.42299</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0.44288</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0.45774</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0.43665</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0.42622</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0.44792</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0.41776</v>
+      </c>
+      <c r="K134" t="n">
+        <v>0.4008</v>
+      </c>
+      <c r="L134" t="n">
+        <v>0.45723</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0.39937</v>
+      </c>
+      <c r="N134" t="n">
+        <v>0.40707</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0.39897</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0.38883</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>0.38027</v>
+      </c>
+      <c r="R134" t="n">
+        <v>0.37525</v>
+      </c>
+      <c r="S134" t="n">
+        <v>0.36012</v>
+      </c>
+      <c r="T134" t="n">
+        <v>0.35693</v>
+      </c>
+      <c r="U134" t="n">
+        <v>0.3659</v>
+      </c>
+      <c r="V134" t="n">
+        <v>0.37739</v>
+      </c>
+      <c r="W134" t="n">
+        <v>0.3714</v>
+      </c>
+      <c r="X134" t="n">
+        <v>0.36032</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>0.35998</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>0.3659</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>0.38682</v>
+      </c>
+      <c r="AB134" t="n">
+        <v>0.39019</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>0.37978</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>0.36673</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>0.36153</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>0.35524</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>0.37987</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>0.39972</v>
+      </c>
+      <c r="AI134" t="n">
+        <v>0.36719</v>
+      </c>
+      <c r="AJ134" t="n">
+        <v>0.38801</v>
+      </c>
+      <c r="AK134" t="n">
+        <v>0.39299</v>
+      </c>
+      <c r="AL134" t="n">
+        <v>0.38819</v>
+      </c>
+      <c r="AM134" t="n">
+        <v>0.38667</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>0.3517</v>
+      </c>
+      <c r="AO134" t="n">
+        <v>0.36844</v>
+      </c>
+      <c r="AP134" t="n">
+        <v>0.34319</v>
+      </c>
+      <c r="AQ134" t="n">
+        <v>0.32532</v>
+      </c>
+      <c r="AR134" t="n">
+        <v>0.26883</v>
+      </c>
+      <c r="AS134" t="n">
+        <v>0.28749</v>
+      </c>
+      <c r="AT134" t="n">
+        <v>0.15365</v>
+      </c>
+      <c r="AU134" t="n">
+        <v>0.34011</v>
+      </c>
+      <c r="AV134" t="n">
+        <v>0.26472</v>
+      </c>
+      <c r="AW134" t="n">
+        <v>0.34631</v>
+      </c>
+      <c r="AX134" t="n">
+        <v>-0.03735</v>
+      </c>
+      <c r="AY134" t="n">
+        <v>0.30659</v>
+      </c>
+      <c r="AZ134" t="n">
+        <v>0.35086</v>
+      </c>
+      <c r="BA134" t="n">
+        <v>0.40858</v>
+      </c>
+      <c r="BB134" t="n">
+        <v>0.3779</v>
+      </c>
+      <c r="BC134" t="n">
+        <v>0.45497</v>
+      </c>
+      <c r="BD134" t="n">
+        <v>0.41278</v>
+      </c>
+      <c r="BE134" t="n">
+        <v>0.46566</v>
+      </c>
+      <c r="BF134" t="n">
+        <v>0.31449</v>
+      </c>
+      <c r="BG134" t="n">
+        <v>0.30958</v>
+      </c>
+      <c r="BH134" t="n">
+        <v>-0.03586</v>
+      </c>
+      <c r="BI134" t="n">
+        <v>0.18429</v>
+      </c>
+      <c r="BJ134" t="n">
+        <v>0.30338</v>
+      </c>
+      <c r="BK134" t="n">
+        <v>0.2928</v>
+      </c>
+      <c r="BL134" t="n">
+        <v>0.31784</v>
+      </c>
+      <c r="BM134" t="n">
+        <v>0.35285</v>
+      </c>
+      <c r="BN134" t="n">
+        <v>0.35037</v>
+      </c>
+      <c r="BO134" t="n">
+        <v>0.34835</v>
+      </c>
+      <c r="BP134" t="n">
+        <v>0.34851</v>
+      </c>
+      <c r="BQ134" t="n">
+        <v>0.36486</v>
+      </c>
+      <c r="BR134" t="n">
+        <v>0.36575</v>
+      </c>
+      <c r="BS134" t="n">
+        <v>0.35795</v>
+      </c>
+      <c r="BT134" t="n">
+        <v>0.39804</v>
+      </c>
+      <c r="BU134" t="n">
+        <v>0.4082</v>
+      </c>
+      <c r="BV134" t="n">
+        <v>0.3625</v>
+      </c>
+      <c r="BW134" t="n">
+        <v>0.40924</v>
+      </c>
+      <c r="BX134" t="n">
+        <v>0.3994</v>
+      </c>
+      <c r="BY134" t="n">
+        <v>0.39075</v>
+      </c>
+      <c r="BZ134" t="n">
+        <v>0.37029</v>
+      </c>
+      <c r="CA134" t="n">
+        <v>0.35454</v>
+      </c>
+      <c r="CB134" t="n">
+        <v>0.37768</v>
+      </c>
+      <c r="CC134" t="n">
+        <v>0.38493</v>
+      </c>
+      <c r="CD134" t="n">
+        <v>0.40524</v>
+      </c>
+      <c r="CE134" t="n">
+        <v>0.39998</v>
+      </c>
+      <c r="CF134" t="n">
+        <v>0.34385</v>
+      </c>
+      <c r="CG134" t="n">
+        <v>0.36444</v>
+      </c>
+      <c r="CH134" t="n">
+        <v>0.37832</v>
+      </c>
+      <c r="CI134" t="n">
+        <v>0.40006</v>
+      </c>
+      <c r="CJ134" t="n">
+        <v>0.36012</v>
+      </c>
+      <c r="CK134" t="n">
+        <v>0.37978</v>
+      </c>
+      <c r="CL134" t="n">
+        <v>0.35512</v>
+      </c>
+      <c r="CM134" t="n">
+        <v>0.39981</v>
+      </c>
+      <c r="CN134" t="n">
+        <v>0.38084</v>
+      </c>
+      <c r="CO134" t="n">
+        <v>0.37512</v>
+      </c>
+      <c r="CP134" t="n">
+        <v>0.36068</v>
+      </c>
+      <c r="CQ134" t="n">
+        <v>0.39378</v>
+      </c>
+      <c r="CR134" t="n">
+        <v>0.37897</v>
+      </c>
+      <c r="CS134" t="n">
+        <v>0.36401</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="B135" t="n">
+        <v>0.33161</v>
+      </c>
+      <c r="C135" t="n">
+        <v>0.44366</v>
+      </c>
+      <c r="D135" t="n">
+        <v>0.35638</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0.37552</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0.37598</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0.35593</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0.37708</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0.35098</v>
+      </c>
+      <c r="J135" t="n">
+        <v>0.37725</v>
+      </c>
+      <c r="K135" t="n">
+        <v>0.3651</v>
+      </c>
+      <c r="L135" t="n">
+        <v>0.35627</v>
+      </c>
+      <c r="M135" t="n">
+        <v>0.35412</v>
+      </c>
+      <c r="N135" t="n">
+        <v>0.35168</v>
+      </c>
+      <c r="O135" t="n">
+        <v>0.35763</v>
+      </c>
+      <c r="P135" t="n">
+        <v>0.34782</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>0.35045</v>
+      </c>
+      <c r="R135" t="n">
+        <v>0.34869</v>
+      </c>
+      <c r="S135" t="n">
+        <v>0.33984</v>
+      </c>
+      <c r="T135" t="n">
+        <v>0.33174</v>
+      </c>
+      <c r="U135" t="n">
+        <v>0.33994</v>
+      </c>
+      <c r="V135" t="n">
+        <v>0.34061</v>
+      </c>
+      <c r="W135" t="n">
+        <v>0.33574</v>
+      </c>
+      <c r="X135" t="n">
+        <v>0.34075</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>0.34576</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>0.33142</v>
+      </c>
+      <c r="AA135" t="n">
+        <v>0.33077</v>
+      </c>
+      <c r="AB135" t="n">
+        <v>0.33937</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>0.33947</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>0.34565</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>0.32686</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>0.31786</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>0.31213</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>0.32599</v>
+      </c>
+      <c r="AI135" t="n">
+        <v>0.24135</v>
+      </c>
+      <c r="AJ135" t="n">
+        <v>0.32791</v>
+      </c>
+      <c r="AK135" t="n">
+        <v>0.32244</v>
+      </c>
+      <c r="AL135" t="n">
+        <v>0.31684</v>
+      </c>
+      <c r="AM135" t="n">
+        <v>0.23267</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>0.29441</v>
+      </c>
+      <c r="AO135" t="n">
+        <v>0.23413</v>
+      </c>
+      <c r="AP135" t="n">
+        <v>0.23425</v>
+      </c>
+      <c r="AQ135" t="n">
+        <v>0.2477</v>
+      </c>
+      <c r="AR135" t="n">
+        <v>0.0025</v>
+      </c>
+      <c r="AS135" t="n">
+        <v>0.13093</v>
+      </c>
+      <c r="AT135" t="n">
+        <v>0.23114</v>
+      </c>
+      <c r="AU135" t="n">
+        <v>0.28788</v>
+      </c>
+      <c r="AV135" t="n">
+        <v>0.01011</v>
+      </c>
+      <c r="AW135" t="n">
+        <v>0.1598</v>
+      </c>
+      <c r="AX135" t="n">
+        <v>0.04343</v>
+      </c>
+      <c r="AY135" t="n">
+        <v>0.25614</v>
+      </c>
+      <c r="AZ135" t="n">
+        <v>-0.004730000000000001</v>
+      </c>
+      <c r="BA135" t="n">
+        <v>0.14507</v>
+      </c>
+      <c r="BB135" t="n">
+        <v>0.15329</v>
+      </c>
+      <c r="BC135" t="n">
+        <v>0.02958</v>
+      </c>
+      <c r="BD135" t="n">
+        <v>0.30319</v>
+      </c>
+      <c r="BE135" t="n">
+        <v>-0.04068</v>
+      </c>
+      <c r="BF135" t="n">
+        <v>0.21563</v>
+      </c>
+      <c r="BG135" t="n">
+        <v>0.22616</v>
+      </c>
+      <c r="BH135" t="n">
+        <v>0.14922</v>
+      </c>
+      <c r="BI135" t="n">
+        <v>0.21124</v>
+      </c>
+      <c r="BJ135" t="n">
+        <v>0.26527</v>
+      </c>
+      <c r="BK135" t="n">
+        <v>0.2835299999999999</v>
+      </c>
+      <c r="BL135" t="n">
+        <v>0.25856</v>
+      </c>
+      <c r="BM135" t="n">
+        <v>0.2964</v>
+      </c>
+      <c r="BN135" t="n">
+        <v>0.32613</v>
+      </c>
+      <c r="BO135" t="n">
+        <v>0.28581</v>
+      </c>
+      <c r="BP135" t="n">
+        <v>0.34954</v>
+      </c>
+      <c r="BQ135" t="n">
+        <v>0.34644</v>
+      </c>
+      <c r="BR135" t="n">
+        <v>0.34995</v>
+      </c>
+      <c r="BS135" t="n">
+        <v>0.34907</v>
+      </c>
+      <c r="BT135" t="n">
+        <v>0.34803</v>
+      </c>
+      <c r="BU135" t="n">
+        <v>0.32694</v>
+      </c>
+      <c r="BV135" t="n">
+        <v>0.33097</v>
+      </c>
+      <c r="BW135" t="n">
+        <v>0.35907</v>
+      </c>
+      <c r="BX135" t="n">
+        <v>0.34922</v>
+      </c>
+      <c r="BY135" t="n">
+        <v>0.34348</v>
+      </c>
+      <c r="BZ135" t="n">
+        <v>0.30892</v>
+      </c>
+      <c r="CA135" t="n">
+        <v>0.3501</v>
+      </c>
+      <c r="CB135" t="n">
+        <v>0.35465</v>
+      </c>
+      <c r="CC135" t="n">
+        <v>0.36606</v>
+      </c>
+      <c r="CD135" t="n">
+        <v>0.35325</v>
+      </c>
+      <c r="CE135" t="n">
+        <v>0.35985</v>
+      </c>
+      <c r="CF135" t="n">
+        <v>0.36383</v>
+      </c>
+      <c r="CG135" t="n">
+        <v>0.35835</v>
+      </c>
+      <c r="CH135" t="n">
+        <v>0.34479</v>
+      </c>
+      <c r="CI135" t="n">
+        <v>0.3592</v>
+      </c>
+      <c r="CJ135" t="n">
+        <v>0.37196</v>
+      </c>
+      <c r="CK135" t="n">
+        <v>0.34335</v>
+      </c>
+      <c r="CL135" t="n">
+        <v>0.3662</v>
+      </c>
+      <c r="CM135" t="n">
+        <v>0.37095</v>
+      </c>
+      <c r="CN135" t="n">
+        <v>0.3608</v>
+      </c>
+      <c r="CO135" t="n">
+        <v>0.35051</v>
+      </c>
+      <c r="CP135" t="n">
+        <v>0.35085</v>
+      </c>
+      <c r="CQ135" t="n">
+        <v>0.35036</v>
+      </c>
+      <c r="CR135" t="n">
+        <v>0.35082</v>
+      </c>
+      <c r="CS135" t="n">
+        <v>0.35226</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="B136" t="n">
+        <v>0.32341</v>
+      </c>
+      <c r="C136" t="n">
+        <v>0.32438</v>
+      </c>
+      <c r="D136" t="n">
+        <v>0.33899</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0.34293</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0.33918</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0.34016</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0.33234</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0.3258</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0.32069</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0.32034</v>
+      </c>
+      <c r="L136" t="n">
+        <v>0.31138</v>
+      </c>
+      <c r="M136" t="n">
+        <v>0.3108</v>
+      </c>
+      <c r="N136" t="n">
+        <v>0.31561</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0.3108399999999999</v>
+      </c>
+      <c r="P136" t="n">
+        <v>0.3118</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>0.31161</v>
+      </c>
+      <c r="R136" t="n">
+        <v>0.31144</v>
+      </c>
+      <c r="S136" t="n">
+        <v>0.31828</v>
+      </c>
+      <c r="T136" t="n">
+        <v>0.30744</v>
+      </c>
+      <c r="U136" t="n">
+        <v>0.30743</v>
+      </c>
+      <c r="V136" t="n">
+        <v>0.30994</v>
+      </c>
+      <c r="W136" t="n">
+        <v>0.311</v>
+      </c>
+      <c r="X136" t="n">
+        <v>0.30679</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>0.30744</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>0.30806</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>0.3108399999999999</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>0.31204</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>0.29159</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>0.22574</v>
+      </c>
+      <c r="AE136" t="n">
+        <v>0.21582</v>
+      </c>
+      <c r="AF136" t="n">
+        <v>0.15039</v>
+      </c>
+      <c r="AG136" t="n">
+        <v>0.17898</v>
+      </c>
+      <c r="AH136" t="n">
+        <v>0.05196</v>
+      </c>
+      <c r="AI136" t="n">
+        <v>0.0159</v>
+      </c>
+      <c r="AJ136" t="n">
+        <v>-0.00179</v>
+      </c>
+      <c r="AK136" t="n">
+        <v>-0.04337</v>
+      </c>
+      <c r="AL136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AM136" t="n">
+        <v>0.05736</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>-0.03406</v>
+      </c>
+      <c r="AO136" t="n">
+        <v>-0.04176</v>
+      </c>
+      <c r="AP136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AQ136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AR136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AS136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AV136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BA136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BB136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BC136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BD136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BE136" t="n">
+        <v>-0.03472</v>
+      </c>
+      <c r="BF136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BG136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BI136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ136" t="n">
+        <v>-0.04489</v>
+      </c>
+      <c r="BK136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BM136" t="n">
+        <v>-0.04869</v>
+      </c>
+      <c r="BN136" t="n">
+        <v>0.03627</v>
+      </c>
+      <c r="BO136" t="n">
+        <v>0.16855</v>
+      </c>
+      <c r="BP136" t="n">
+        <v>0.21394</v>
+      </c>
+      <c r="BQ136" t="n">
+        <v>0.27655</v>
+      </c>
+      <c r="BR136" t="n">
+        <v>0.24371</v>
+      </c>
+      <c r="BS136" t="n">
+        <v>0.24494</v>
+      </c>
+      <c r="BT136" t="n">
+        <v>0.24543</v>
+      </c>
+      <c r="BU136" t="n">
+        <v>0.24981</v>
+      </c>
+      <c r="BV136" t="n">
+        <v>0.26263</v>
+      </c>
+      <c r="BW136" t="n">
+        <v>0.28603</v>
+      </c>
+      <c r="BX136" t="n">
+        <v>0.27127</v>
+      </c>
+      <c r="BY136" t="n">
+        <v>0.26767</v>
+      </c>
+      <c r="BZ136" t="n">
+        <v>0.25625</v>
+      </c>
+      <c r="CA136" t="n">
+        <v>0.30328</v>
+      </c>
+      <c r="CB136" t="n">
+        <v>0.2759</v>
+      </c>
+      <c r="CC136" t="n">
+        <v>0.27952</v>
+      </c>
+      <c r="CD136" t="n">
+        <v>0.26437</v>
+      </c>
+      <c r="CE136" t="n">
+        <v>0.27911</v>
+      </c>
+      <c r="CF136" t="n">
+        <v>0.26685</v>
+      </c>
+      <c r="CG136" t="n">
+        <v>0.28295</v>
+      </c>
+      <c r="CH136" t="n">
+        <v>0.27274</v>
+      </c>
+      <c r="CI136" t="n">
+        <v>0.29228</v>
+      </c>
+      <c r="CJ136" t="n">
+        <v>0.35987</v>
+      </c>
+      <c r="CK136" t="n">
+        <v>0.29949</v>
+      </c>
+      <c r="CL136" t="n">
+        <v>0.30382</v>
+      </c>
+      <c r="CM136" t="n">
+        <v>0.28404</v>
+      </c>
+      <c r="CN136" t="n">
+        <v>0.25388</v>
+      </c>
+      <c r="CO136" t="n">
+        <v>0.26567</v>
+      </c>
+      <c r="CP136" t="n">
+        <v>0.24993</v>
+      </c>
+      <c r="CQ136" t="n">
+        <v>0.233</v>
+      </c>
+      <c r="CR136" t="n">
+        <v>0.17609</v>
+      </c>
+      <c r="CS136" t="n">
+        <v>0.05267</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B137" t="n">
+        <v>0.29794</v>
+      </c>
+      <c r="C137" t="n">
+        <v>0.40285</v>
+      </c>
+      <c r="D137" t="n">
+        <v>0.00566</v>
+      </c>
+      <c r="E137" t="n">
+        <v>0.06108</v>
+      </c>
+      <c r="F137" t="n">
+        <v>0.24588</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0.22274</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0.22247</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0.14043</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0.26838</v>
+      </c>
+      <c r="K137" t="n">
+        <v>0.25978</v>
+      </c>
+      <c r="L137" t="n">
+        <v>0.24212</v>
+      </c>
+      <c r="M137" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="N137" t="n">
+        <v>0.20443</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0.18743</v>
+      </c>
+      <c r="P137" t="n">
+        <v>0.21146</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>0.22464</v>
+      </c>
+      <c r="R137" t="n">
+        <v>0.16757</v>
+      </c>
+      <c r="S137" t="n">
+        <v>0.1874</v>
+      </c>
+      <c r="T137" t="n">
+        <v>0.22192</v>
+      </c>
+      <c r="U137" t="n">
+        <v>0.21777</v>
+      </c>
+      <c r="V137" t="n">
+        <v>0.24304</v>
+      </c>
+      <c r="W137" t="n">
+        <v>0.23041</v>
+      </c>
+      <c r="X137" t="n">
+        <v>0.21344</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>0.26001</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>0.22371</v>
+      </c>
+      <c r="AA137" t="n">
+        <v>0.26731</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>0.32594</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>0.26943</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>0.24529</v>
+      </c>
+      <c r="AE137" t="n">
+        <v>0.24813</v>
+      </c>
+      <c r="AF137" t="n">
+        <v>0.18214</v>
+      </c>
+      <c r="AG137" t="n">
+        <v>0.06089</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>0.48633</v>
+      </c>
+      <c r="AI137" t="n">
+        <v>0.49427</v>
+      </c>
+      <c r="AJ137" t="n">
+        <v>0.54057</v>
+      </c>
+      <c r="AK137" t="n">
+        <v>0.36843</v>
+      </c>
+      <c r="AL137" t="n">
+        <v>0.06863</v>
+      </c>
+      <c r="AM137" t="n">
+        <v>0.22218</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>-0.02649</v>
+      </c>
+      <c r="AO137" t="n">
+        <v>0.20052</v>
+      </c>
+      <c r="AP137" t="n">
+        <v>0.091</v>
+      </c>
+      <c r="AQ137" t="n">
+        <v>0.03982</v>
+      </c>
+      <c r="AR137" t="n">
+        <v>0.05247</v>
+      </c>
+      <c r="AS137" t="n">
+        <v>-0.01034</v>
+      </c>
+      <c r="AT137" t="n">
+        <v>0.20731</v>
+      </c>
+      <c r="AU137" t="n">
+        <v>0.02919</v>
+      </c>
+      <c r="AV137" t="n">
+        <v>0.28978</v>
+      </c>
+      <c r="AW137" t="n">
+        <v>-0.00414</v>
+      </c>
+      <c r="AX137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ137" t="n">
+        <v>0.02394</v>
+      </c>
+      <c r="BA137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BB137" t="n">
+        <v>0.12909</v>
+      </c>
+      <c r="BC137" t="n">
+        <v>-0.03917</v>
+      </c>
+      <c r="BD137" t="n">
+        <v>0.03784000000000001</v>
+      </c>
+      <c r="BE137" t="n">
+        <v>0.02764</v>
+      </c>
+      <c r="BF137" t="n">
+        <v>0.07903</v>
+      </c>
+      <c r="BG137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH137" t="n">
+        <v>0.02324</v>
+      </c>
+      <c r="BI137" t="n">
+        <v>0.01072</v>
+      </c>
+      <c r="BJ137" t="n">
+        <v>0.02497</v>
+      </c>
+      <c r="BK137" t="n">
+        <v>0.04492</v>
+      </c>
+      <c r="BL137" t="n">
+        <v>0.23262</v>
+      </c>
+      <c r="BM137" t="n">
+        <v>0.27925</v>
+      </c>
+      <c r="BN137" t="n">
+        <v>0.24996</v>
+      </c>
+      <c r="BO137" t="n">
+        <v>0.2778</v>
+      </c>
+      <c r="BP137" t="n">
+        <v>0.30339</v>
+      </c>
+      <c r="BQ137" t="n">
+        <v>0.30523</v>
+      </c>
+      <c r="BR137" t="n">
+        <v>0.30156</v>
+      </c>
+      <c r="BS137" t="n">
+        <v>0.31777</v>
+      </c>
+      <c r="BT137" t="n">
+        <v>0.32161</v>
+      </c>
+      <c r="BU137" t="n">
+        <v>0.3098</v>
+      </c>
+      <c r="BV137" t="n">
+        <v>0.31512</v>
+      </c>
+      <c r="BW137" t="n">
+        <v>0.32809</v>
+      </c>
+      <c r="BX137" t="n">
+        <v>0.32136</v>
+      </c>
+      <c r="BY137" t="n">
+        <v>0.3415899999999999</v>
+      </c>
+      <c r="BZ137" t="n">
+        <v>0.3201</v>
+      </c>
+      <c r="CA137" t="n">
+        <v>0.34069</v>
+      </c>
+      <c r="CB137" t="n">
+        <v>0.3479</v>
+      </c>
+      <c r="CC137" t="n">
+        <v>0.17474</v>
+      </c>
+      <c r="CD137" t="n">
+        <v>0.34232</v>
+      </c>
+      <c r="CE137" t="n">
+        <v>0.34206</v>
+      </c>
+      <c r="CF137" t="n">
+        <v>0.33525</v>
+      </c>
+      <c r="CG137" t="n">
+        <v>0.34938</v>
+      </c>
+      <c r="CH137" t="n">
+        <v>0.34115</v>
+      </c>
+      <c r="CI137" t="n">
+        <v>0.36682</v>
+      </c>
+      <c r="CJ137" t="n">
+        <v>0.33011</v>
+      </c>
+      <c r="CK137" t="n">
+        <v>0.34201</v>
+      </c>
+      <c r="CL137" t="n">
+        <v>0.35086</v>
+      </c>
+      <c r="CM137" t="n">
+        <v>0.31981</v>
+      </c>
+      <c r="CN137" t="n">
+        <v>0.32905</v>
+      </c>
+      <c r="CO137" t="n">
+        <v>0.32976</v>
+      </c>
+      <c r="CP137" t="n">
+        <v>0.33094</v>
+      </c>
+      <c r="CQ137" t="n">
+        <v>0.32809</v>
+      </c>
+      <c r="CR137" t="n">
+        <v>0.33998</v>
+      </c>
+      <c r="CS137" t="n">
+        <v>0.32531</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B138" t="n">
+        <v>0.33022</v>
+      </c>
+      <c r="C138" t="n">
+        <v>0.35522</v>
+      </c>
+      <c r="D138" t="n">
+        <v>0.36719</v>
+      </c>
+      <c r="E138" t="n">
+        <v>0.33317</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0.33643</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0.33565</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0.331</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0.33101</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0.33125</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0.33377</v>
+      </c>
+      <c r="L138" t="n">
+        <v>0.32927</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0.3419</v>
+      </c>
+      <c r="N138" t="n">
+        <v>0.33518</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0.3344</v>
+      </c>
+      <c r="P138" t="n">
+        <v>0.32772</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>0.34461</v>
+      </c>
+      <c r="R138" t="n">
+        <v>0.1112</v>
+      </c>
+      <c r="S138" t="n">
+        <v>0.32668</v>
+      </c>
+      <c r="T138" t="n">
+        <v>0.32718</v>
+      </c>
+      <c r="U138" t="n">
+        <v>0.3213</v>
+      </c>
+      <c r="V138" t="n">
+        <v>0.33147</v>
+      </c>
+      <c r="W138" t="n">
+        <v>0.32886</v>
+      </c>
+      <c r="X138" t="n">
+        <v>0.32972</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>0.33214</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>0.33576</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>0.34335</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>0.24085</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>0.39253</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>0.24146</v>
+      </c>
+      <c r="AE138" t="n">
+        <v>0.30238</v>
+      </c>
+      <c r="AF138" t="n">
+        <v>0.24347</v>
+      </c>
+      <c r="AG138" t="n">
+        <v>0.12045</v>
+      </c>
+      <c r="AH138" t="n">
+        <v>0.23359</v>
+      </c>
+      <c r="AI138" t="n">
+        <v>0.35225</v>
+      </c>
+      <c r="AJ138" t="n">
+        <v>0.28953</v>
+      </c>
+      <c r="AK138" t="n">
+        <v>0.30795</v>
+      </c>
+      <c r="AL138" t="n">
+        <v>0.38877</v>
+      </c>
+      <c r="AM138" t="n">
+        <v>0.30646</v>
+      </c>
+      <c r="AN138" t="n">
+        <v>0.39287</v>
+      </c>
+      <c r="AO138" t="n">
+        <v>0.32953</v>
+      </c>
+      <c r="AP138" t="n">
+        <v>0.3244</v>
+      </c>
+      <c r="AQ138" t="n">
+        <v>0.31447</v>
+      </c>
+      <c r="AR138" t="n">
+        <v>0.33936</v>
+      </c>
+      <c r="AS138" t="n">
+        <v>0.29735</v>
+      </c>
+      <c r="AT138" t="n">
+        <v>0.30889</v>
+      </c>
+      <c r="AU138" t="n">
+        <v>0.30671</v>
+      </c>
+      <c r="AV138" t="n">
+        <v>0.30878</v>
+      </c>
+      <c r="AW138" t="n">
+        <v>0.2899</v>
+      </c>
+      <c r="AX138" t="n">
+        <v>0.11106</v>
+      </c>
+      <c r="AY138" t="n">
+        <v>0.25422</v>
+      </c>
+      <c r="AZ138" t="n">
+        <v>0.26971</v>
+      </c>
+      <c r="BA138" t="n">
+        <v>0.30391</v>
+      </c>
+      <c r="BB138" t="n">
+        <v>0.31075</v>
+      </c>
+      <c r="BC138" t="n">
+        <v>0.16683</v>
+      </c>
+      <c r="BD138" t="n">
+        <v>0.31871</v>
+      </c>
+      <c r="BE138" t="n">
+        <v>0.3162</v>
+      </c>
+      <c r="BF138" t="n">
+        <v>0.14876</v>
+      </c>
+      <c r="BG138" t="n">
+        <v>0.07306</v>
+      </c>
+      <c r="BH138" t="n">
+        <v>0.30887</v>
+      </c>
+      <c r="BI138" t="n">
+        <v>0.29006</v>
+      </c>
+      <c r="BJ138" t="n">
+        <v>0.31025</v>
+      </c>
+      <c r="BK138" t="n">
+        <v>0.31642</v>
+      </c>
+      <c r="BL138" t="n">
+        <v>0.32091</v>
+      </c>
+      <c r="BM138" t="n">
+        <v>0.32644</v>
+      </c>
+      <c r="BN138" t="n">
+        <v>0.33677</v>
+      </c>
+      <c r="BO138" t="n">
+        <v>0.32381</v>
+      </c>
+      <c r="BP138" t="n">
+        <v>0.3470299999999999</v>
+      </c>
+      <c r="BQ138" t="n">
+        <v>0.34029</v>
+      </c>
+      <c r="BR138" t="n">
+        <v>0.33793</v>
+      </c>
+      <c r="BS138" t="n">
+        <v>0.33913</v>
+      </c>
+      <c r="BT138" t="n">
+        <v>0.3404</v>
+      </c>
+      <c r="BU138" t="n">
+        <v>0.34508</v>
+      </c>
+      <c r="BV138" t="n">
+        <v>0.33133</v>
+      </c>
+      <c r="BW138" t="n">
+        <v>0.34803</v>
+      </c>
+      <c r="BX138" t="n">
+        <v>0.34671</v>
+      </c>
+      <c r="BY138" t="n">
+        <v>0.33378</v>
+      </c>
+      <c r="BZ138" t="n">
+        <v>0.34372</v>
+      </c>
+      <c r="CA138" t="n">
+        <v>0.33996</v>
+      </c>
+      <c r="CB138" t="n">
+        <v>0.34408</v>
+      </c>
+      <c r="CC138" t="n">
+        <v>0.37169</v>
+      </c>
+      <c r="CD138" t="n">
+        <v>0.31589</v>
+      </c>
+      <c r="CE138" t="n">
+        <v>0.31265</v>
+      </c>
+      <c r="CF138" t="n">
+        <v>0.3579</v>
+      </c>
+      <c r="CG138" t="n">
+        <v>0.38092</v>
+      </c>
+      <c r="CH138" t="n">
+        <v>0.34102</v>
+      </c>
+      <c r="CI138" t="n">
+        <v>0.35223</v>
+      </c>
+      <c r="CJ138" t="n">
+        <v>0.34725</v>
+      </c>
+      <c r="CK138" t="n">
+        <v>0.35271</v>
+      </c>
+      <c r="CL138" t="n">
+        <v>0.34642</v>
+      </c>
+      <c r="CM138" t="n">
+        <v>0.36805</v>
+      </c>
+      <c r="CN138" t="n">
+        <v>0.35248</v>
+      </c>
+      <c r="CO138" t="n">
+        <v>0.31473</v>
+      </c>
+      <c r="CP138" t="n">
+        <v>0.33214</v>
+      </c>
+      <c r="CQ138" t="n">
+        <v>0.32609</v>
+      </c>
+      <c r="CR138" t="n">
+        <v>0.33093</v>
+      </c>
+      <c r="CS138" t="n">
+        <v>0.3312</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B139" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="C139" t="n">
+        <v>0.37069</v>
+      </c>
+      <c r="D139" t="n">
+        <v>0.33109</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0.33108</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0.2624</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0.31652</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0.32025</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0.32828</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0.32935</v>
+      </c>
+      <c r="K139" t="n">
+        <v>0.33078</v>
+      </c>
+      <c r="L139" t="n">
+        <v>0.33186</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0.33567</v>
+      </c>
+      <c r="N139" t="n">
+        <v>0.3452</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0.2872</v>
+      </c>
+      <c r="P139" t="n">
+        <v>0.3494</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>0.34083</v>
+      </c>
+      <c r="R139" t="n">
+        <v>0.33629</v>
+      </c>
+      <c r="S139" t="n">
+        <v>0.32107</v>
+      </c>
+      <c r="T139" t="n">
+        <v>0.32078</v>
+      </c>
+      <c r="U139" t="n">
+        <v>0.3313</v>
+      </c>
+      <c r="V139" t="n">
+        <v>0.34662</v>
+      </c>
+      <c r="W139" t="n">
+        <v>0.33124</v>
+      </c>
+      <c r="X139" t="n">
+        <v>0.34034</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>0.35417</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>0.32335</v>
+      </c>
+      <c r="AA139" t="n">
+        <v>0.36948</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>0.35543</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>0.36976</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>0.35952</v>
+      </c>
+      <c r="AE139" t="n">
+        <v>0.34747</v>
+      </c>
+      <c r="AF139" t="n">
+        <v>0.26437</v>
+      </c>
+      <c r="AG139" t="n">
+        <v>0.33009</v>
+      </c>
+      <c r="AH139" t="n">
+        <v>0.34086</v>
+      </c>
+      <c r="AI139" t="n">
+        <v>0.33696</v>
+      </c>
+      <c r="AJ139" t="n">
+        <v>0.4983</v>
+      </c>
+      <c r="AK139" t="n">
+        <v>0.2811</v>
+      </c>
+      <c r="AL139" t="n">
+        <v>0.50371</v>
+      </c>
+      <c r="AM139" t="n">
+        <v>0.24138</v>
+      </c>
+      <c r="AN139" t="n">
+        <v>0.28527</v>
+      </c>
+      <c r="AO139" t="n">
+        <v>0.30831</v>
+      </c>
+      <c r="AP139" t="n">
+        <v>0.3435</v>
+      </c>
+      <c r="AQ139" t="n">
+        <v>0.28658</v>
+      </c>
+      <c r="AR139" t="n">
+        <v>0.26025</v>
+      </c>
+      <c r="AS139" t="n">
+        <v>0.2808</v>
+      </c>
+      <c r="AT139" t="n">
+        <v>0.27139</v>
+      </c>
+      <c r="AU139" t="n">
+        <v>0.25564</v>
+      </c>
+      <c r="AV139" t="n">
+        <v>0.14034</v>
+      </c>
+      <c r="AW139" t="n">
+        <v>0.25618</v>
+      </c>
+      <c r="AX139" t="n">
+        <v>0.30779</v>
+      </c>
+      <c r="AY139" t="n">
+        <v>0.36745</v>
+      </c>
+      <c r="AZ139" t="n">
+        <v>0.27798</v>
+      </c>
+      <c r="BA139" t="n">
+        <v>0.2544</v>
+      </c>
+      <c r="BB139" t="n">
+        <v>0.25723</v>
+      </c>
+      <c r="BC139" t="n">
+        <v>0.28667</v>
+      </c>
+      <c r="BD139" t="n">
+        <v>0.34475</v>
+      </c>
+      <c r="BE139" t="n">
+        <v>0.34758</v>
+      </c>
+      <c r="BF139" t="n">
+        <v>0.32682</v>
+      </c>
+      <c r="BG139" t="n">
+        <v>0.23244</v>
+      </c>
+      <c r="BH139" t="n">
+        <v>0.27208</v>
+      </c>
+      <c r="BI139" t="n">
+        <v>0.31709</v>
+      </c>
+      <c r="BJ139" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="BK139" t="n">
+        <v>0.26516</v>
+      </c>
+      <c r="BL139" t="n">
+        <v>0.26846</v>
+      </c>
+      <c r="BM139" t="n">
+        <v>0.29021</v>
+      </c>
+      <c r="BN139" t="n">
+        <v>0.34598</v>
+      </c>
+      <c r="BO139" t="n">
+        <v>0.41735</v>
+      </c>
+      <c r="BP139" t="n">
+        <v>0.39929</v>
+      </c>
+      <c r="BQ139" t="n">
+        <v>0.46542</v>
+      </c>
+      <c r="BR139" t="n">
+        <v>0.47839</v>
+      </c>
+      <c r="BS139" t="n">
+        <v>0.45949</v>
+      </c>
+      <c r="BT139" t="n">
+        <v>0.4745</v>
+      </c>
+      <c r="BU139" t="n">
+        <v>0.37781</v>
+      </c>
+      <c r="BV139" t="n">
+        <v>-0.02564</v>
+      </c>
+      <c r="BW139" t="n">
+        <v>0.3738</v>
+      </c>
+      <c r="BX139" t="n">
+        <v>0.40396</v>
+      </c>
+      <c r="BY139" t="n">
+        <v>0.43506</v>
+      </c>
+      <c r="BZ139" t="n">
+        <v>0.31596</v>
+      </c>
+      <c r="CA139" t="n">
+        <v>0.39758</v>
+      </c>
+      <c r="CB139" t="n">
+        <v>0.3435299999999999</v>
+      </c>
+      <c r="CC139" t="n">
+        <v>0.47248</v>
+      </c>
+      <c r="CD139" t="n">
+        <v>0.43254</v>
+      </c>
+      <c r="CE139" t="n">
+        <v>0.3732</v>
+      </c>
+      <c r="CF139" t="n">
+        <v>0.41794</v>
+      </c>
+      <c r="CG139" t="n">
+        <v>0.42592</v>
+      </c>
+      <c r="CH139" t="n">
+        <v>0.74537</v>
+      </c>
+      <c r="CI139" t="n">
+        <v>0.45161</v>
+      </c>
+      <c r="CJ139" t="n">
+        <v>0.40738</v>
+      </c>
+      <c r="CK139" t="n">
+        <v>0.45935</v>
+      </c>
+      <c r="CL139" t="n">
+        <v>0.40178</v>
+      </c>
+      <c r="CM139" t="n">
+        <v>0.37981</v>
+      </c>
+      <c r="CN139" t="n">
+        <v>0.38816</v>
+      </c>
+      <c r="CO139" t="n">
+        <v>0.36786</v>
+      </c>
+      <c r="CP139" t="n">
+        <v>0.36769</v>
+      </c>
+      <c r="CQ139" t="n">
+        <v>0.37277</v>
+      </c>
+      <c r="CR139" t="n">
+        <v>0.36862</v>
+      </c>
+      <c r="CS139" t="n">
+        <v>0.36898</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B140" t="n">
+        <v>0.34706</v>
+      </c>
+      <c r="C140" t="n">
+        <v>0.46615</v>
+      </c>
+      <c r="D140" t="n">
+        <v>0.40036</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0.40042</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0.39075</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0.38083</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0.36022</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0.37568</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0.37451</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0.37874</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0.37745</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0.36929</v>
+      </c>
+      <c r="N140" t="n">
+        <v>0.36698</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0.36161</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0.36005</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>0.3599</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0.36045</v>
+      </c>
+      <c r="S140" t="n">
+        <v>0.356</v>
+      </c>
+      <c r="T140" t="n">
+        <v>0.32915</v>
+      </c>
+      <c r="U140" t="n">
+        <v>0.35624</v>
+      </c>
+      <c r="V140" t="n">
+        <v>0.35129</v>
+      </c>
+      <c r="W140" t="n">
+        <v>0.34987</v>
+      </c>
+      <c r="X140" t="n">
+        <v>0.3473</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>0.35016</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>0.3604</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>0.37127</v>
+      </c>
+      <c r="AB140" t="n">
+        <v>0.40009</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>0.37604</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>0.36938</v>
+      </c>
+      <c r="AE140" t="n">
+        <v>0.34948</v>
+      </c>
+      <c r="AF140" t="n">
+        <v>0.3373</v>
+      </c>
+      <c r="AG140" t="n">
+        <v>0.28846</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>0.33712</v>
+      </c>
+      <c r="AI140" t="n">
+        <v>0.29788</v>
+      </c>
+      <c r="AJ140" t="n">
+        <v>0.3018</v>
+      </c>
+      <c r="AK140" t="n">
+        <v>0.27907</v>
+      </c>
+      <c r="AL140" t="n">
+        <v>0.378</v>
+      </c>
+      <c r="AM140" t="n">
+        <v>0.32166</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>0.28916</v>
+      </c>
+      <c r="AO140" t="n">
+        <v>0.34494</v>
+      </c>
+      <c r="AP140" t="n">
+        <v>0.18835</v>
+      </c>
+      <c r="AQ140" t="n">
+        <v>0.33045</v>
+      </c>
+      <c r="AR140" t="n">
+        <v>0.15349</v>
+      </c>
+      <c r="AS140" t="n">
+        <v>0.34272</v>
+      </c>
+      <c r="AT140" t="n">
+        <v>0.23129</v>
+      </c>
+      <c r="AU140" t="n">
+        <v>0.34968</v>
+      </c>
+      <c r="AV140" t="n">
+        <v>0.3325</v>
+      </c>
+      <c r="AW140" t="n">
+        <v>0.33298</v>
+      </c>
+      <c r="AX140" t="n">
+        <v>0.29233</v>
+      </c>
+      <c r="AY140" t="n">
+        <v>0.28932</v>
+      </c>
+      <c r="AZ140" t="n">
+        <v>0.30738</v>
+      </c>
+      <c r="BA140" t="n">
+        <v>0.31129</v>
+      </c>
+      <c r="BB140" t="n">
+        <v>0.25556</v>
+      </c>
+      <c r="BC140" t="n">
+        <v>0.31951</v>
+      </c>
+      <c r="BD140" t="n">
+        <v>0.33807</v>
+      </c>
+      <c r="BE140" t="n">
+        <v>0.33313</v>
+      </c>
+      <c r="BF140" t="n">
+        <v>0.1742</v>
+      </c>
+      <c r="BG140" t="n">
+        <v>0.2901</v>
+      </c>
+      <c r="BH140" t="n">
+        <v>0.2566000000000001</v>
+      </c>
+      <c r="BI140" t="n">
+        <v>0.26441</v>
+      </c>
+      <c r="BJ140" t="n">
+        <v>0.30144</v>
+      </c>
+      <c r="BK140" t="n">
+        <v>0.30596</v>
+      </c>
+      <c r="BL140" t="n">
+        <v>0.30966</v>
+      </c>
+      <c r="BM140" t="n">
+        <v>0.33995</v>
+      </c>
+      <c r="BN140" t="n">
+        <v>0.32929</v>
+      </c>
+      <c r="BO140" t="n">
+        <v>0.34375</v>
+      </c>
+      <c r="BP140" t="n">
+        <v>0.32635</v>
+      </c>
+      <c r="BQ140" t="n">
+        <v>0.35924</v>
+      </c>
+      <c r="BR140" t="n">
+        <v>0.43202</v>
+      </c>
+      <c r="BS140" t="n">
+        <v>0.35884</v>
+      </c>
+      <c r="BT140" t="n">
+        <v>0.40577</v>
+      </c>
+      <c r="BU140" t="n">
+        <v>0.38977</v>
+      </c>
+      <c r="BV140" t="n">
+        <v>0.38611</v>
+      </c>
+      <c r="BW140" t="n">
+        <v>0.46025</v>
+      </c>
+      <c r="BX140" t="n">
+        <v>0.55751</v>
+      </c>
+      <c r="BY140" t="n">
+        <v>0.55364</v>
+      </c>
+      <c r="BZ140" t="n">
+        <v>0.37993</v>
+      </c>
+      <c r="CA140" t="n">
+        <v>0.4581</v>
+      </c>
+      <c r="CB140" t="n">
+        <v>0.54691</v>
+      </c>
+      <c r="CC140" t="n">
+        <v>0.45942</v>
+      </c>
+      <c r="CD140" t="n">
+        <v>0.34911</v>
+      </c>
+      <c r="CE140" t="n">
+        <v>0.49161</v>
+      </c>
+      <c r="CF140" t="n">
+        <v>0.39548</v>
+      </c>
+      <c r="CG140" t="n">
+        <v>0.53199</v>
+      </c>
+      <c r="CH140" t="n">
+        <v>0.5229</v>
+      </c>
+      <c r="CI140" t="n">
+        <v>0.72825</v>
+      </c>
+      <c r="CJ140" t="n">
+        <v>0.77015</v>
+      </c>
+      <c r="CK140" t="n">
+        <v>0.54571</v>
+      </c>
+      <c r="CL140" t="n">
+        <v>0.54787</v>
+      </c>
+      <c r="CM140" t="n">
+        <v>0.39867</v>
+      </c>
+      <c r="CN140" t="n">
+        <v>0.44341</v>
+      </c>
+      <c r="CO140" t="n">
+        <v>0.38869</v>
+      </c>
+      <c r="CP140" t="n">
+        <v>0.37431</v>
+      </c>
+      <c r="CQ140" t="n">
+        <v>0.37941</v>
+      </c>
+      <c r="CR140" t="n">
+        <v>0.37001</v>
+      </c>
+      <c r="CS140" t="n">
+        <v>0.37567</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B141" t="n">
+        <v>0.2733</v>
+      </c>
+      <c r="C141" t="n">
+        <v>0.36989</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0.31887</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0.3713</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0.33524</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0.33813</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0.35078</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0.32118</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0.3351</v>
+      </c>
+      <c r="K141" t="n">
+        <v>0.34385</v>
+      </c>
+      <c r="L141" t="n">
+        <v>0.33892</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0.33976</v>
+      </c>
+      <c r="N141" t="n">
+        <v>0.34531</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0.3359</v>
+      </c>
+      <c r="P141" t="n">
+        <v>0.33774</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>0.3364</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0.31398</v>
+      </c>
+      <c r="S141" t="n">
+        <v>0.32779</v>
+      </c>
+      <c r="T141" t="n">
+        <v>0.31976</v>
+      </c>
+      <c r="U141" t="n">
+        <v>0.30936</v>
+      </c>
+      <c r="V141" t="n">
+        <v>0.30456</v>
+      </c>
+      <c r="W141" t="n">
+        <v>0.30863</v>
+      </c>
+      <c r="X141" t="n">
+        <v>0.30913</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>0.29184</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>0.29125</v>
+      </c>
+      <c r="AA141" t="n">
+        <v>0.34521</v>
+      </c>
+      <c r="AB141" t="n">
+        <v>0.36336</v>
+      </c>
+      <c r="AC141" t="n">
+        <v>0.30363</v>
+      </c>
+      <c r="AD141" t="n">
+        <v>0.28983</v>
+      </c>
+      <c r="AE141" t="n">
+        <v>0.28521</v>
+      </c>
+      <c r="AF141" t="n">
+        <v>0.27954</v>
+      </c>
+      <c r="AG141" t="n">
+        <v>0.27301</v>
+      </c>
+      <c r="AH141" t="n">
+        <v>0.31354</v>
+      </c>
+      <c r="AI141" t="n">
+        <v>0.25826</v>
+      </c>
+      <c r="AJ141" t="n">
+        <v>0.25797</v>
+      </c>
+      <c r="AK141" t="n">
+        <v>0.27406</v>
+      </c>
+      <c r="AL141" t="n">
+        <v>0.20797</v>
+      </c>
+      <c r="AM141" t="n">
+        <v>0.23237</v>
+      </c>
+      <c r="AN141" t="n">
+        <v>0.13886</v>
+      </c>
+      <c r="AO141" t="n">
+        <v>-0.0161</v>
+      </c>
+      <c r="AP141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AQ141" t="n">
+        <v>0.13771</v>
+      </c>
+      <c r="AR141" t="n">
+        <v>0.01058</v>
+      </c>
+      <c r="AS141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT141" t="n">
+        <v>0.10761</v>
+      </c>
+      <c r="AU141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AV141" t="n">
+        <v>-0.01349</v>
+      </c>
+      <c r="AW141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX141" t="n">
+        <v>-0.04114</v>
+      </c>
+      <c r="AY141" t="n">
+        <v>-0.02477</v>
+      </c>
+      <c r="AZ141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BA141" t="n">
+        <v>0.23363</v>
+      </c>
+      <c r="BB141" t="n">
+        <v>-0.04146</v>
+      </c>
+      <c r="BC141" t="n">
+        <v>0.0203</v>
+      </c>
+      <c r="BD141" t="n">
+        <v>0.03309</v>
+      </c>
+      <c r="BE141" t="n">
+        <v>0.02417</v>
+      </c>
+      <c r="BF141" t="n">
+        <v>0.01351</v>
+      </c>
+      <c r="BG141" t="n">
+        <v>0.01234</v>
+      </c>
+      <c r="BH141" t="n">
+        <v>0.02836</v>
+      </c>
+      <c r="BI141" t="n">
+        <v>0.11983</v>
+      </c>
+      <c r="BJ141" t="n">
+        <v>0.06594</v>
+      </c>
+      <c r="BK141" t="n">
+        <v>0.12956</v>
+      </c>
+      <c r="BL141" t="n">
+        <v>0.14649</v>
+      </c>
+      <c r="BM141" t="n">
+        <v>0.17853</v>
+      </c>
+      <c r="BN141" t="n">
+        <v>0.24341</v>
+      </c>
+      <c r="BO141" t="n">
+        <v>0.18876</v>
+      </c>
+      <c r="BP141" t="n">
+        <v>0.15779</v>
+      </c>
+      <c r="BQ141" t="n">
+        <v>0.32682</v>
+      </c>
+      <c r="BR141" t="n">
+        <v>0.29558</v>
+      </c>
+      <c r="BS141" t="n">
+        <v>0.31028</v>
+      </c>
+      <c r="BT141" t="n">
+        <v>0.31062</v>
+      </c>
+      <c r="BU141" t="n">
+        <v>0.34188</v>
+      </c>
+      <c r="BV141" t="n">
+        <v>0.2226</v>
+      </c>
+      <c r="BW141" t="n">
+        <v>0.32342</v>
+      </c>
+      <c r="BX141" t="n">
+        <v>0.33365</v>
+      </c>
+      <c r="BY141" t="n">
+        <v>0.32875</v>
+      </c>
+      <c r="BZ141" t="n">
+        <v>0.2702</v>
+      </c>
+      <c r="CA141" t="n">
+        <v>0.36365</v>
+      </c>
+      <c r="CB141" t="n">
+        <v>0.38489</v>
+      </c>
+      <c r="CC141" t="n">
+        <v>0.35964</v>
+      </c>
+      <c r="CD141" t="n">
+        <v>0.36641</v>
+      </c>
+      <c r="CE141" t="n">
+        <v>0.33854</v>
+      </c>
+      <c r="CF141" t="n">
+        <v>0.39374</v>
+      </c>
+      <c r="CG141" t="n">
+        <v>0.37598</v>
+      </c>
+      <c r="CH141" t="n">
+        <v>0.37509</v>
+      </c>
+      <c r="CI141" t="n">
+        <v>0.40054</v>
+      </c>
+      <c r="CJ141" t="n">
+        <v>0.38164</v>
+      </c>
+      <c r="CK141" t="n">
+        <v>0.36105</v>
+      </c>
+      <c r="CL141" t="n">
+        <v>0.35397</v>
+      </c>
+      <c r="CM141" t="n">
+        <v>0.36072</v>
+      </c>
+      <c r="CN141" t="n">
+        <v>0.41487</v>
+      </c>
+      <c r="CO141" t="n">
+        <v>0.37996</v>
+      </c>
+      <c r="CP141" t="n">
+        <v>0.37635</v>
+      </c>
+      <c r="CQ141" t="n">
+        <v>0.3759</v>
+      </c>
+      <c r="CR141" t="n">
+        <v>0.38812</v>
+      </c>
+      <c r="CS141" t="n">
+        <v>0.37842</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B142" t="n">
+        <v>0.35296</v>
+      </c>
+      <c r="C142" t="n">
+        <v>0.8039400000000001</v>
+      </c>
+      <c r="D142" t="n">
+        <v>0.34107</v>
+      </c>
+      <c r="E142" t="n">
+        <v>0.40017</v>
+      </c>
+      <c r="F142" t="n">
+        <v>0.37839</v>
+      </c>
+      <c r="G142" t="n">
+        <v>0.33594</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0.33866</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0.35413</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0.35214</v>
+      </c>
+      <c r="K142" t="n">
+        <v>0.38348</v>
+      </c>
+      <c r="L142" t="n">
+        <v>0.34588</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0.34716</v>
+      </c>
+      <c r="N142" t="n">
+        <v>0.34239</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0.38152</v>
+      </c>
+      <c r="P142" t="n">
+        <v>0.35545</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>0.36212</v>
+      </c>
+      <c r="R142" t="n">
+        <v>0.38043</v>
+      </c>
+      <c r="S142" t="n">
+        <v>0.37922</v>
+      </c>
+      <c r="T142" t="n">
+        <v>0.34796</v>
+      </c>
+      <c r="U142" t="n">
+        <v>0.36103</v>
+      </c>
+      <c r="V142" t="n">
+        <v>0.36379</v>
+      </c>
+      <c r="W142" t="n">
+        <v>0.36186</v>
+      </c>
+      <c r="X142" t="n">
+        <v>0.36528</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>0.35603</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>0.36701</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>0.35226</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>0.36645</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>0.34065</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>0.32062</v>
+      </c>
+      <c r="AE142" t="n">
+        <v>0.32333</v>
+      </c>
+      <c r="AF142" t="n">
+        <v>0.30312</v>
+      </c>
+      <c r="AG142" t="n">
+        <v>0.30307</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>0.29584</v>
+      </c>
+      <c r="AI142" t="n">
+        <v>0.29047</v>
+      </c>
+      <c r="AJ142" t="n">
+        <v>0.27712</v>
+      </c>
+      <c r="AK142" t="n">
+        <v>0.25442</v>
+      </c>
+      <c r="AL142" t="n">
+        <v>0.24491</v>
+      </c>
+      <c r="AM142" t="n">
+        <v>0.21561</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>0.21511</v>
+      </c>
+      <c r="AO142" t="n">
+        <v>0.21931</v>
+      </c>
+      <c r="AP142" t="n">
+        <v>0.24003</v>
+      </c>
+      <c r="AQ142" t="n">
+        <v>0.08295</v>
+      </c>
+      <c r="AR142" t="n">
+        <v>0.007160000000000001</v>
+      </c>
+      <c r="AS142" t="n">
+        <v>0.004759999999999999</v>
+      </c>
+      <c r="AT142" t="n">
+        <v>0.004019999999999999</v>
+      </c>
+      <c r="AU142" t="n">
+        <v>0.03482</v>
+      </c>
+      <c r="AV142" t="n">
+        <v>0.11313</v>
+      </c>
+      <c r="AW142" t="n">
+        <v>0.02613</v>
+      </c>
+      <c r="AX142" t="n">
+        <v>-0.00405</v>
+      </c>
+      <c r="AY142" t="n">
+        <v>0.01383</v>
+      </c>
+      <c r="AZ142" t="n">
+        <v>0.04479</v>
+      </c>
+      <c r="BA142" t="n">
+        <v>0.01312</v>
+      </c>
+      <c r="BB142" t="n">
+        <v>0.01232</v>
+      </c>
+      <c r="BC142" t="n">
+        <v>0.01978</v>
+      </c>
+      <c r="BD142" t="n">
+        <v>0.15679</v>
+      </c>
+      <c r="BE142" t="n">
+        <v>0.17452</v>
+      </c>
+      <c r="BF142" t="n">
+        <v>0.02911</v>
+      </c>
+      <c r="BG142" t="n">
+        <v>0.16304</v>
+      </c>
+      <c r="BH142" t="n">
+        <v>0.13369</v>
+      </c>
+      <c r="BI142" t="n">
+        <v>0.15044</v>
+      </c>
+      <c r="BJ142" t="n">
+        <v>0.17613</v>
+      </c>
+      <c r="BK142" t="n">
+        <v>0.13189</v>
+      </c>
+      <c r="BL142" t="n">
+        <v>0.21598</v>
+      </c>
+      <c r="BM142" t="n">
+        <v>0.19279</v>
+      </c>
+      <c r="BN142" t="n">
+        <v>0.24619</v>
+      </c>
+      <c r="BO142" t="n">
+        <v>0.22318</v>
+      </c>
+      <c r="BP142" t="n">
+        <v>0.26761</v>
+      </c>
+      <c r="BQ142" t="n">
+        <v>0.30746</v>
+      </c>
+      <c r="BR142" t="n">
+        <v>0.28838</v>
+      </c>
+      <c r="BS142" t="n">
+        <v>0.42877</v>
+      </c>
+      <c r="BT142" t="n">
+        <v>0.38319</v>
+      </c>
+      <c r="BU142" t="n">
+        <v>0.39544</v>
+      </c>
+      <c r="BV142" t="n">
+        <v>0.36163</v>
+      </c>
+      <c r="BW142" t="n">
+        <v>0.38357</v>
+      </c>
+      <c r="BX142" t="n">
+        <v>0.40132</v>
+      </c>
+      <c r="BY142" t="n">
+        <v>0.35723</v>
+      </c>
+      <c r="BZ142" t="n">
+        <v>0.35438</v>
+      </c>
+      <c r="CA142" t="n">
+        <v>0.38388</v>
+      </c>
+      <c r="CB142" t="n">
+        <v>0.5198400000000001</v>
+      </c>
+      <c r="CC142" t="n">
+        <v>0.41179</v>
+      </c>
+      <c r="CD142" t="n">
+        <v>0.38658</v>
+      </c>
+      <c r="CE142" t="n">
+        <v>0.38969</v>
+      </c>
+      <c r="CF142" t="n">
+        <v>0.39315</v>
+      </c>
+      <c r="CG142" t="n">
+        <v>0.38787</v>
+      </c>
+      <c r="CH142" t="n">
+        <v>0.38203</v>
+      </c>
+      <c r="CI142" t="n">
+        <v>0.40315</v>
+      </c>
+      <c r="CJ142" t="n">
+        <v>0.35606</v>
+      </c>
+      <c r="CK142" t="n">
+        <v>0.38821</v>
+      </c>
+      <c r="CL142" t="n">
+        <v>0.4263</v>
+      </c>
+      <c r="CM142" t="n">
+        <v>0.38671</v>
+      </c>
+      <c r="CN142" t="n">
+        <v>0.38791</v>
+      </c>
+      <c r="CO142" t="n">
+        <v>0.37998</v>
+      </c>
+      <c r="CP142" t="n">
+        <v>0.3846</v>
+      </c>
+      <c r="CQ142" t="n">
+        <v>0.37409</v>
+      </c>
+      <c r="CR142" t="n">
+        <v>0.36217</v>
+      </c>
+      <c r="CS142" t="n">
+        <v>0.38669</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B143" t="n">
+        <v>0.32902</v>
+      </c>
+      <c r="C143" t="n">
+        <v>0.5195299999999999</v>
+      </c>
+      <c r="D143" t="n">
+        <v>0.39208</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0.39528</v>
+      </c>
+      <c r="F143" t="n">
+        <v>0.31491</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0.36981</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0.35975</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0.36622</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0.34625</v>
+      </c>
+      <c r="K143" t="n">
+        <v>0.41963</v>
+      </c>
+      <c r="L143" t="n">
+        <v>0.34494</v>
+      </c>
+      <c r="M143" t="n">
+        <v>0.37647</v>
+      </c>
+      <c r="N143" t="n">
+        <v>0.37331</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0.34243</v>
+      </c>
+      <c r="P143" t="n">
+        <v>0.34104</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>0.35015</v>
+      </c>
+      <c r="R143" t="n">
+        <v>0.3335</v>
+      </c>
+      <c r="S143" t="n">
+        <v>0.31686</v>
+      </c>
+      <c r="T143" t="n">
+        <v>0.35038</v>
+      </c>
+      <c r="U143" t="n">
+        <v>0.3235</v>
+      </c>
+      <c r="V143" t="n">
+        <v>0.32062</v>
+      </c>
+      <c r="W143" t="n">
+        <v>0.33294</v>
+      </c>
+      <c r="X143" t="n">
+        <v>0.36451</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>0.34023</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>0.35394</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>0.34074</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>0.3497</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>0.34168</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>0.32333</v>
+      </c>
+      <c r="AE143" t="n">
+        <v>0.29163</v>
+      </c>
+      <c r="AF143" t="n">
+        <v>0.25399</v>
+      </c>
+      <c r="AG143" t="n">
+        <v>0.21756</v>
+      </c>
+      <c r="AH143" t="n">
+        <v>0.19842</v>
+      </c>
+      <c r="AI143" t="n">
+        <v>0.12736</v>
+      </c>
+      <c r="AJ143" t="n">
+        <v>0.17564</v>
+      </c>
+      <c r="AK143" t="n">
+        <v>0.2021</v>
+      </c>
+      <c r="AL143" t="n">
+        <v>0.19564</v>
+      </c>
+      <c r="AM143" t="n">
+        <v>0.10164</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>0.12599</v>
+      </c>
+      <c r="AO143" t="n">
+        <v>0.05371</v>
+      </c>
+      <c r="AP143" t="n">
+        <v>0.08315</v>
+      </c>
+      <c r="AQ143" t="n">
+        <v>0.03749</v>
+      </c>
+      <c r="AR143" t="n">
+        <v>0.03851</v>
+      </c>
+      <c r="AS143" t="n">
+        <v>0.03836</v>
+      </c>
+      <c r="AT143" t="n">
+        <v>0.03715</v>
+      </c>
+      <c r="AU143" t="n">
+        <v>0.04562</v>
+      </c>
+      <c r="AV143" t="n">
+        <v>0.05158</v>
+      </c>
+      <c r="AW143" t="n">
+        <v>0.06809</v>
+      </c>
+      <c r="AX143" t="n">
+        <v>0.03487</v>
+      </c>
+      <c r="AY143" t="n">
+        <v>0.06156</v>
+      </c>
+      <c r="AZ143" t="n">
+        <v>0.08425000000000001</v>
+      </c>
+      <c r="BA143" t="n">
+        <v>0.13988</v>
+      </c>
+      <c r="BB143" t="n">
+        <v>0.17412</v>
+      </c>
+      <c r="BC143" t="n">
+        <v>0.10197</v>
+      </c>
+      <c r="BD143" t="n">
+        <v>0.20644</v>
+      </c>
+      <c r="BE143" t="n">
+        <v>0.18161</v>
+      </c>
+      <c r="BF143" t="n">
+        <v>0.10548</v>
+      </c>
+      <c r="BG143" t="n">
+        <v>0.04788000000000001</v>
+      </c>
+      <c r="BH143" t="n">
+        <v>0.23554</v>
+      </c>
+      <c r="BI143" t="n">
+        <v>0.11938</v>
+      </c>
+      <c r="BJ143" t="n">
+        <v>0.10429</v>
+      </c>
+      <c r="BK143" t="n">
+        <v>0.20931</v>
+      </c>
+      <c r="BL143" t="n">
+        <v>0.15646</v>
+      </c>
+      <c r="BM143" t="n">
+        <v>0.1789</v>
+      </c>
+      <c r="BN143" t="n">
+        <v>0.20284</v>
+      </c>
+      <c r="BO143" t="n">
+        <v>0.17293</v>
+      </c>
+      <c r="BP143" t="n">
+        <v>0.21059</v>
+      </c>
+      <c r="BQ143" t="n">
+        <v>0.23418</v>
+      </c>
+      <c r="BR143" t="n">
+        <v>0.23521</v>
+      </c>
+      <c r="BS143" t="n">
+        <v>0.25108</v>
+      </c>
+      <c r="BT143" t="n">
+        <v>0.27701</v>
+      </c>
+      <c r="BU143" t="n">
+        <v>0.2810299999999999</v>
+      </c>
+      <c r="BV143" t="n">
+        <v>0.28327</v>
+      </c>
+      <c r="BW143" t="n">
+        <v>0.30558</v>
+      </c>
+      <c r="BX143" t="n">
+        <v>0.35969</v>
+      </c>
+      <c r="BY143" t="n">
+        <v>0.39259</v>
+      </c>
+      <c r="BZ143" t="n">
+        <v>0.3400899999999999</v>
+      </c>
+      <c r="CA143" t="n">
+        <v>0.32713</v>
+      </c>
+      <c r="CB143" t="n">
+        <v>0.29585</v>
+      </c>
+      <c r="CC143" t="n">
+        <v>0.34679</v>
+      </c>
+      <c r="CD143" t="n">
+        <v>0.38565</v>
+      </c>
+      <c r="CE143" t="n">
+        <v>0.37302</v>
+      </c>
+      <c r="CF143" t="n">
+        <v>0.3771600000000001</v>
+      </c>
+      <c r="CG143" t="n">
+        <v>0.36485</v>
+      </c>
+      <c r="CH143" t="n">
+        <v>0.38564</v>
+      </c>
+      <c r="CI143" t="n">
+        <v>0.40781</v>
+      </c>
+      <c r="CJ143" t="n">
+        <v>0.41514</v>
+      </c>
+      <c r="CK143" t="n">
+        <v>0.4933</v>
+      </c>
+      <c r="CL143" t="n">
+        <v>0.40555</v>
+      </c>
+      <c r="CM143" t="n">
+        <v>0.41296</v>
+      </c>
+      <c r="CN143" t="n">
+        <v>0.43057</v>
+      </c>
+      <c r="CO143" t="n">
+        <v>0.41094</v>
+      </c>
+      <c r="CP143" t="n">
+        <v>0.39233</v>
+      </c>
+      <c r="CQ143" t="n">
+        <v>0.40852</v>
+      </c>
+      <c r="CR143" t="n">
+        <v>0.40969</v>
+      </c>
+      <c r="CS143" t="n">
+        <v>0.38406</v>
       </c>
     </row>
   </sheetData>
